--- a/ready-for-annotation/de/abcnews.199762.xlsx
+++ b/ready-for-annotation/de/abcnews.199762.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="326">
   <si>
     <t>ID</t>
   </si>
@@ -59,7 +59,7 @@
     <t>auffinden</t>
   </si>
   <si>
-    <t>28- jähriger Koch in San Francisco Mall tot aufgefunden Ein 28- jähriger Koch , der vor kurzem nach San Francisco gezogen ist , wurde im in dem Treppenhaus eines örtlichen Einkaufzentrums tot aufgefunden .</t>
+    <t>28- jähriger Koch in San Francisco Mall tot aufgefunden</t>
   </si>
   <si>
     <t>file://conllu/de/abcnews.199762.conllu#s1_0</t>
@@ -68,6 +68,18 @@
     <t>2</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>Ein 28- jähriger Koch , der vor kurzem nach San Francisco gezogen ist , wurde im in dem Treppenhaus eines örtlichen Einkaufzentrums tot aufgefunden .</t>
+  </si>
+  <si>
+    <t>file://conllu/de/abcnews.199762.conllu#s2_0</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
@@ -77,13 +89,10 @@
     <t>Der Bruder des Opfers sagte aus , dass er sich niemanden vorstellen kann , der ihm schaden wollen würde , &amp;quot; Endlich ging es bei ihm wieder bergauf . &amp;quot;</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s2_0</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s3_0</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>identifizieren</t>
@@ -92,10 +101,10 @@
     <t>Der am an dem Mittwoch morgen in der Westfield Mall gefundene Leichnam wurde als der 28 Jahre alte Frank Galicia aus San Francisco identifiziert , teilte die gerichtsmedizinische Abteilung in San Francisco mit .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s3_0</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s4_0</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>6</t>
@@ -107,10 +116,7 @@
     <t>Das San Francisco Police Department sagte , dass der Tod als Mord eingestuft wurde und die Ermittlungen am an dem Laufen sind .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s4_0</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s5_0</t>
   </si>
   <si>
     <t>teilen</t>
@@ -119,7 +125,7 @@
     <t>Der Bruder des Opfers , Louis Galicia , teilte dem ABS Sender KGO in San Francisco mit , dass Frank , der früher als Koch in Boston gearbeitet hat , vor sechs Monaten seinen Traumjob als Koch im in dem Sons &amp;amp; Daughters Restaurant in San Francisco ergattert hatte .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s5_0</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s6_0</t>
   </si>
   <si>
     <t>7</t>
@@ -128,7 +134,10 @@
     <t>Ein Sprecher des Sons &amp;amp; Daughters sagte , dass sie über seinen Tod &amp;quot; schockiert und am an dem Boden zerstört seien &amp;quot; .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s6_0</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s7_0</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>sein (sein Team)</t>
@@ -137,10 +146,7 @@
     <t>&amp;quot; Wir sind ein kleines Team , das wie eine enge Familie arbeitet und wir werden ihn schmerzlich vermissen , &amp;quot; sagte der Sprecher weiter .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s7_0</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s8_0</t>
   </si>
   <si>
     <t>sein</t>
@@ -149,7 +155,10 @@
     <t>Unsere Gedanken und unser Beileid sind in dieser schweren Zeit bei Franks Familie und Freunden .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s8_0</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s9_0</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>geben</t>
@@ -158,10 +167,10 @@
     <t>Louis Galicia gab an , dass Frank zunächst in Hostels lebte , aber dass , &amp;quot; die Dinge für ihn endlich bergauf gingen . &amp;quot;</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s9_0</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s10_0</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>finden</t>
@@ -170,16 +179,16 @@
     <t>&amp;quot; Er fand eine Wohnung , er hatte eine Freundin , &amp;quot; teilte Louis Garcia KGO mit .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s10_0</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s11_0</t>
   </si>
   <si>
     <t>Louis Galicia sagte , dass er sich niemanden vorstellen könne , der seinem jüngeren Bruder schaden wollen würde .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s11_0</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s12_0</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>sein (sein Mensch)</t>
@@ -188,10 +197,10 @@
     <t>Er war ein freundlicher Mensch mit einem großen Herzen .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s12_0</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s13_0</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>sein (sein verbinden)</t>
@@ -200,10 +209,10 @@
     <t>Seine Art mit seiner Familie zu verbinden war es , uns immer etwas zu kochen , uns das Abendessen zuzubereiten , &amp;quot; sagte Louis Galicia .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s13_0</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s14_0</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>teilnehmen</t>
@@ -212,10 +221,10 @@
     <t>Er wollte nie an irgendeiner Art von Auseinandersetzung teilnehmen .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s14_0</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s15_0</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>sein (sein Bruder)</t>
@@ -224,10 +233,10 @@
     <t>Er war der Bruder , der mit dem Strom schwamm .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s15_0</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s16_0</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>25</t>
@@ -236,10 +245,10 @@
     <t>&amp;quot; Bei allem , was in der Welt schief läuft , war er dieser ungeschliffene Diamant , der jeden Tag hell leuchtete , &amp;quot; sagte er .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s16_0</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s17_0</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>haben</t>
@@ -248,7 +257,7 @@
     <t>Jeder , der Informationen zu dem Fall hat , wird gebeten das Hinweistelefon des SFPD unter der Nummer 415-575-4444 anzurufen .</t>
   </si>
   <si>
-    <t>file://conllu/de/abcnews.199762.conllu#s17_0</t>
+    <t>file://conllu/de/abcnews.199762.conllu#s18_0</t>
   </si>
   <si>
     <t>WORD</t>
@@ -284,7 +293,7 @@
     <t>REF_DIST_ANTE</t>
   </si>
   <si>
-    <t># text = 28-jähriger Koch in San Francisco Mall tot aufgefunden Ein 28-jähriger Koch, der vor kurzem nach San Francisco gezogen ist, wurde im Treppenhaus eines örtlichen Einkaufzentrums tot aufgefunden.</t>
+    <t># text = 28-jähriger Koch in San Francisco Mall tot aufgefunden</t>
   </si>
   <si>
     <t>28-</t>
@@ -326,265 +335,268 @@
     <t>aufgefunden</t>
   </si>
   <si>
+    <t># text = Ein 28-jähriger Koch, der vor kurzem nach San Francisco gezogen ist, wurde im Treppenhaus eines örtlichen Einkaufzentrums tot aufgefunden.</t>
+  </si>
+  <si>
     <t>Ein</t>
   </si>
   <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>der</t>
+  </si>
+  <si>
+    <t>SBJ_3</t>
+  </si>
+  <si>
+    <t>pron</t>
+  </si>
+  <si>
+    <t>vor</t>
+  </si>
+  <si>
+    <t>kurzem</t>
+  </si>
+  <si>
+    <t>other_3</t>
+  </si>
+  <si>
+    <t>indef-np.bare</t>
+  </si>
+  <si>
+    <t>nach</t>
+  </si>
+  <si>
+    <t>other_4</t>
+  </si>
+  <si>
+    <t>gezogen</t>
+  </si>
+  <si>
+    <t>ist</t>
+  </si>
+  <si>
+    <t>wurde</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>Treppenhaus</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>def-np.the</t>
+  </si>
+  <si>
+    <t>eines</t>
+  </si>
+  <si>
+    <t>örtlichen</t>
+  </si>
+  <si>
+    <t>Einkaufzentrums</t>
+  </si>
+  <si>
+    <t>indef-np.a</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t># text = Der Bruder des Opfers sagte aus, dass er sich niemanden vorstellen kann, der ihm schaden wollen würde, \"Endlich ging es bei ihm wieder bergauf.\"</t>
+  </si>
+  <si>
+    <t>Der</t>
+  </si>
+  <si>
+    <t>Bruder</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>Opfers</t>
+  </si>
+  <si>
+    <t>sagte</t>
+  </si>
+  <si>
+    <t>aus</t>
+  </si>
+  <si>
+    <t>dass</t>
+  </si>
+  <si>
+    <t>er</t>
+  </si>
+  <si>
+    <t>SBJ_2</t>
+  </si>
+  <si>
+    <t>pron.pper</t>
+  </si>
+  <si>
+    <t>sich</t>
+  </si>
+  <si>
+    <t>OBJ_2</t>
+  </si>
+  <si>
+    <t>niemanden</t>
+  </si>
+  <si>
+    <t>pron.pind</t>
+  </si>
+  <si>
+    <t>vorstellen</t>
+  </si>
+  <si>
+    <t>kann</t>
+  </si>
+  <si>
+    <t>ihm</t>
+  </si>
+  <si>
+    <t>schaden</t>
+  </si>
+  <si>
+    <t>wollen</t>
+  </si>
+  <si>
+    <t>würde</t>
+  </si>
+  <si>
+    <t>&amp;quot;</t>
+  </si>
+  <si>
+    <t>Endlich</t>
+  </si>
+  <si>
+    <t>ging</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>bei</t>
+  </si>
+  <si>
+    <t>wieder</t>
+  </si>
+  <si>
+    <t>bergauf</t>
+  </si>
+  <si>
+    <t># text = Der am Mittwoch morgen in der Westfield Mall gefundene Leichnam wurde als der 28 Jahre alte Frank Galicia aus San Francisco identifiziert, teilte die gerichtsmedizinische Abteilung in San Francisco mit.</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
+    <t>Mittwoch</t>
+  </si>
+  <si>
+    <t>morgen</t>
+  </si>
+  <si>
+    <t>Westfield</t>
+  </si>
+  <si>
+    <t>gefundene</t>
+  </si>
+  <si>
+    <t>Leichnam</t>
+  </si>
+  <si>
+    <t>als</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Jahre</t>
+  </si>
+  <si>
+    <t>indef-np.quant</t>
+  </si>
+  <si>
+    <t>alte</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>Galicia</t>
+  </si>
+  <si>
+    <t>identifiziert</t>
+  </si>
+  <si>
+    <t>teilte</t>
+  </si>
+  <si>
+    <t>die</t>
+  </si>
+  <si>
+    <t>gerichtsmedizinische</t>
+  </si>
+  <si>
+    <t>Abteilung</t>
+  </si>
+  <si>
+    <t>mit</t>
+  </si>
+  <si>
+    <t># text = Das San Francisco Police Department sagte, dass der Tod als Mord eingestuft wurde und die Ermittlungen am Laufen sind.</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>Police</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Tod</t>
+  </si>
+  <si>
+    <t>Mord</t>
+  </si>
+  <si>
+    <t>eingestuft</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>Ermittlungen</t>
+  </si>
+  <si>
+    <t>Laufen</t>
+  </si>
+  <si>
+    <t>sind</t>
+  </si>
+  <si>
+    <t># text = Der Bruder des Opfers, Louis Galicia, teilte dem ABS Sender KGO in San Francisco mit, dass Frank, der früher als Koch in Boston gearbeitet hat, vor sechs Monaten seinen Traumjob als Koch im Sons &amp; Daughters Restaurant in San Francisco ergattert hatte.</t>
+  </si>
+  <si>
+    <t>Louis</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
     <t>OBJ</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>der</t>
-  </si>
-  <si>
-    <t>SBJ_3</t>
-  </si>
-  <si>
-    <t>pron</t>
-  </si>
-  <si>
-    <t>vor</t>
-  </si>
-  <si>
-    <t>kurzem</t>
-  </si>
-  <si>
-    <t>other_3</t>
-  </si>
-  <si>
-    <t>indef-np.bare</t>
-  </si>
-  <si>
-    <t>nach</t>
-  </si>
-  <si>
-    <t>other_4</t>
-  </si>
-  <si>
-    <t>gezogen</t>
-  </si>
-  <si>
-    <t>ist</t>
-  </si>
-  <si>
-    <t>wurde</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>Treppenhaus</t>
-  </si>
-  <si>
-    <t>def-np.the</t>
-  </si>
-  <si>
-    <t>eines</t>
-  </si>
-  <si>
-    <t>örtlichen</t>
-  </si>
-  <si>
-    <t>Einkaufzentrums</t>
-  </si>
-  <si>
-    <t>indef-np.a</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>--</t>
-  </si>
-  <si>
-    <t># text = Der Bruder des Opfers sagte aus, dass er sich niemanden vorstellen kann, der ihm schaden wollen würde, \"Endlich ging es bei ihm wieder bergauf.\"</t>
-  </si>
-  <si>
-    <t>Der</t>
-  </si>
-  <si>
-    <t>Bruder</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>Opfers</t>
-  </si>
-  <si>
-    <t>sagte</t>
-  </si>
-  <si>
-    <t>aus</t>
-  </si>
-  <si>
-    <t>dass</t>
-  </si>
-  <si>
-    <t>er</t>
-  </si>
-  <si>
-    <t>SBJ_2</t>
-  </si>
-  <si>
-    <t>pron.pper</t>
-  </si>
-  <si>
-    <t>sich</t>
-  </si>
-  <si>
-    <t>OBJ_2</t>
-  </si>
-  <si>
-    <t>niemanden</t>
-  </si>
-  <si>
-    <t>pron.pind</t>
-  </si>
-  <si>
-    <t>vorstellen</t>
-  </si>
-  <si>
-    <t>kann</t>
-  </si>
-  <si>
-    <t>ihm</t>
-  </si>
-  <si>
-    <t>schaden</t>
-  </si>
-  <si>
-    <t>wollen</t>
-  </si>
-  <si>
-    <t>würde</t>
-  </si>
-  <si>
-    <t>&amp;quot;</t>
-  </si>
-  <si>
-    <t>Endlich</t>
-  </si>
-  <si>
-    <t>ging</t>
-  </si>
-  <si>
-    <t>es</t>
-  </si>
-  <si>
-    <t>bei</t>
-  </si>
-  <si>
-    <t>wieder</t>
-  </si>
-  <si>
-    <t>bergauf</t>
-  </si>
-  <si>
-    <t># text = Der am Mittwoch morgen in der Westfield Mall gefundene Leichnam wurde als der 28 Jahre alte Frank Galicia aus San Francisco identifiziert, teilte die gerichtsmedizinische Abteilung in San Francisco mit.</t>
-  </si>
-  <si>
-    <t>an</t>
-  </si>
-  <si>
-    <t>Mittwoch</t>
-  </si>
-  <si>
-    <t>morgen</t>
-  </si>
-  <si>
-    <t>Westfield</t>
-  </si>
-  <si>
-    <t>gefundene</t>
-  </si>
-  <si>
-    <t>Leichnam</t>
-  </si>
-  <si>
-    <t>als</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Jahre</t>
-  </si>
-  <si>
-    <t>indef-np.quant</t>
-  </si>
-  <si>
-    <t>alte</t>
-  </si>
-  <si>
-    <t>Frank</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>Galicia</t>
-  </si>
-  <si>
-    <t>identifiziert</t>
-  </si>
-  <si>
-    <t>teilte</t>
-  </si>
-  <si>
-    <t>die</t>
-  </si>
-  <si>
-    <t>gerichtsmedizinische</t>
-  </si>
-  <si>
-    <t>Abteilung</t>
-  </si>
-  <si>
-    <t>mit</t>
-  </si>
-  <si>
-    <t># text = Das San Francisco Police Department sagte, dass der Tod als Mord eingestuft wurde und die Ermittlungen am Laufen sind.</t>
-  </si>
-  <si>
-    <t>Das</t>
-  </si>
-  <si>
-    <t>Police</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Tod</t>
-  </si>
-  <si>
-    <t>Mord</t>
-  </si>
-  <si>
-    <t>eingestuft</t>
-  </si>
-  <si>
-    <t>und</t>
-  </si>
-  <si>
-    <t>Ermittlungen</t>
-  </si>
-  <si>
-    <t>Laufen</t>
-  </si>
-  <si>
-    <t>sind</t>
-  </si>
-  <si>
-    <t># text = Der Bruder des Opfers, Louis Galicia, teilte dem ABS Sender KGO in San Francisco mit, dass Frank, der früher als Koch in Boston gearbeitet hat, vor sechs Monaten seinen Traumjob als Koch im Sons &amp; Daughters Restaurant in San Francisco ergattert hatte.</t>
-  </si>
-  <si>
-    <t>Louis</t>
-  </si>
-  <si>
-    <t>ABS</t>
   </si>
   <si>
     <t>Sender</t>
@@ -1456,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="60" customHeight="1"/>
   <cols>
     <col min="2" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1542,13 +1554,13 @@
         <v>12</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="9">
         <f>IF(A3=1,"_",IF(C3="_","???",C3))</f>
@@ -1564,22 +1576,22 @@
     </row>
     <row r="4" spans="1:10" ht="60" customHeight="1">
       <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="G4" s="9">
         <f>IF(A4=1,"_",IF(C4="_","???",C4))</f>
@@ -1595,22 +1607,22 @@
     </row>
     <row r="5" spans="1:10" ht="60" customHeight="1">
       <c r="A5" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="G5" s="9">
         <f>IF(A5=1,"_",IF(C5="_","???",C5))</f>
@@ -1626,22 +1638,22 @@
     </row>
     <row r="6" spans="1:10" ht="60" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="G6" s="9">
         <f>IF(A6=1,"_",IF(C6="_","???",C6))</f>
@@ -1657,22 +1669,22 @@
     </row>
     <row r="7" spans="1:10" ht="60" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="G7" s="9">
         <f>IF(A7=1,"_",IF(C7="_","???",C7))</f>
@@ -1688,22 +1700,22 @@
     </row>
     <row r="8" spans="1:10" ht="60" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="G8" s="9">
         <f>IF(A8=1,"_",IF(C8="_","???",C8))</f>
@@ -1719,22 +1731,22 @@
     </row>
     <row r="9" spans="1:10" ht="60" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="G9" s="9">
         <f>IF(A9=1,"_",IF(C9="_","???",C9))</f>
@@ -1753,19 +1765,19 @@
         <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="G10" s="9">
         <f>IF(A10=1,"_",IF(C10="_","???",C10))</f>
@@ -1781,22 +1793,22 @@
     </row>
     <row r="11" spans="1:10" ht="60" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>51</v>
       </c>
       <c r="G11" s="9">
         <f>IF(A11=1,"_",IF(C11="_","???",C11))</f>
@@ -1812,16 +1824,16 @@
     </row>
     <row r="12" spans="1:10" ht="60" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>53</v>
@@ -1843,22 +1855,22 @@
     </row>
     <row r="13" spans="1:10" ht="60" customHeight="1">
       <c r="A13" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="G13" s="9">
         <f>IF(A13=1,"_",IF(C13="_","???",C13))</f>
@@ -1874,22 +1886,22 @@
     </row>
     <row r="14" spans="1:10" ht="60" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="G14" s="9">
         <f>IF(A14=1,"_",IF(C14="_","???",C14))</f>
@@ -1905,22 +1917,22 @@
     </row>
     <row r="15" spans="1:10" ht="60" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="G15" s="9">
         <f>IF(A15=1,"_",IF(C15="_","???",C15))</f>
@@ -1936,22 +1948,22 @@
     </row>
     <row r="16" spans="1:10" ht="60" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="G16" s="9">
         <f>IF(A16=1,"_",IF(C16="_","???",C16))</f>
@@ -1967,22 +1979,22 @@
     </row>
     <row r="17" spans="1:10" ht="60" customHeight="1">
       <c r="A17" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="G17" s="9">
         <f>IF(A17=1,"_",IF(C17="_","???",C17))</f>
@@ -1998,22 +2010,22 @@
     </row>
     <row r="18" spans="1:10" ht="60" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="G18" s="9">
         <f>IF(A18=1,"_",IF(C18="_","???",C18))</f>
@@ -2026,6 +2038,37 @@
         <v>12</v>
       </c>
       <c r="J18" s="12"/>
+    </row>
+    <row r="19" spans="1:10" ht="60" customHeight="1">
+      <c r="A19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="9">
+        <f>IF(A19=1,"_",IF(C19="_","???",C19))</f>
+        <v/>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="12"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
@@ -2035,7 +2078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L441"/>
+  <dimension ref="A1:L443"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2047,37 +2090,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H1" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I1" s="18" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>9</v>
@@ -2085,12 +2128,12 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" s="21">
         <f>IF(D3="?OLD","!!!","")</f>
@@ -2124,7 +2167,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E4" s="21">
         <f>IF(D4="?OLD","!!!","")</f>
@@ -2158,16 +2201,16 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E5" s="21">
         <f>IF(D5="?OLD","!!!","")</f>
@@ -2201,7 +2244,7 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E6" s="21">
         <f>IF(D6="?OLD","!!!","")</f>
@@ -2235,16 +2278,16 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E7" s="21">
         <f>IF(D7="?OLD","!!!","")</f>
@@ -2278,7 +2321,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E8" s="21">
         <f>IF(D8="?OLD","!!!","")</f>
@@ -2312,7 +2355,7 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E9" s="21">
         <f>IF(D9="?OLD","!!!","")</f>
@@ -2346,7 +2389,7 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E10" s="21">
         <f>IF(D10="?OLD","!!!","")</f>
@@ -2380,7 +2423,7 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E11" s="21">
         <f>IF(D11="?OLD","!!!","")</f>
@@ -2413,76 +2456,16 @@
       <c r="L11" s="26"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="E12" s="21">
-        <f>IF(D12="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F12" s="22" t="str">
-        <f>IF(OR(E12="",E12="!!!"),"",IF(NOT(ISNA(VLOOKUP(E12,E$1:E11,1,FALSE()))),"OLD",IF(AND(E12&lt;&gt;"",E12&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G12" s="23" t="str">
-        <f>IF(OR(E12="",E12="!!!"),"",IF(OR(J12=0,AND(J12=1,K12=1),AND(J12=1,I12="SBJ"),AND(J12=1,I12=0)),"?IN_FOCUS",IF(J12&lt;=2,"?ACTIVATED",IF(J12&lt;&gt;"","?FAMILIAR",IF(F12="NEW",IF(ISNA(VLOOKUP(E12,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H12" s="24" t="str">
-        <f>IF(J12&lt;&gt;1,"",IF(I12="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I12" s="25" t="str">
-        <f>IF(OR(E12="",E12="!!!",F12="NEW"),"",INDEX(B11:B$2,-1+SUMPRODUCT(MAX(ROW(E11:E$2)*(E12=E11:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J12" s="25" t="str">
-        <f>IF(OR(E12="",E12="!!!",F12="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E12)*(E12=E$2:E12)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E11)*(E2=E$1:E11))))))</f>
-        <v> </v>
-      </c>
-      <c r="K12" s="25" t="str">
-        <f>IF(OR(E12="",E12="!!!",F12="NEW"),"",INDEX(J$1:J11,SUMPRODUCT(MAX(ROW(E$1:E11)*(E12=E$1:E11)))))</f>
-        <v> </v>
-      </c>
-      <c r="L12" s="26"/>
+      <c r="A12" s="20"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="21">
-        <f>IF(D13="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F13" s="22" t="str">
-        <f>IF(OR(E13="",E13="!!!"),"",IF(NOT(ISNA(VLOOKUP(E13,E$1:E12,1,FALSE()))),"OLD",IF(AND(E13&lt;&gt;"",E13&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G13" s="23" t="str">
-        <f>IF(OR(E13="",E13="!!!"),"",IF(OR(J13=0,AND(J13=1,K13=1),AND(J13=1,I13="SBJ"),AND(J13=1,I13=0)),"?IN_FOCUS",IF(J13&lt;=2,"?ACTIVATED",IF(J13&lt;&gt;"","?FAMILIAR",IF(F13="NEW",IF(ISNA(VLOOKUP(E13,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H13" s="24" t="str">
-        <f>IF(J13&lt;&gt;1,"",IF(I13="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I13" s="25" t="str">
-        <f>IF(OR(E13="",E13="!!!",F13="NEW"),"",INDEX(B12:B$2,-1+SUMPRODUCT(MAX(ROW(E12:E$2)*(E13=E12:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J13" s="25" t="str">
-        <f>IF(OR(E13="",E13="!!!",F13="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E13)*(E13=E$2:E13)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E12)*(E2=E$1:E12))))))</f>
-        <v> </v>
-      </c>
-      <c r="K13" s="25" t="str">
-        <f>IF(OR(E13="",E13="!!!",F13="NEW"),"",INDEX(J$1:J12,SUMPRODUCT(MAX(ROW(E$1:E12)*(E13=E$1:E12)))))</f>
-        <v> </v>
-      </c>
-      <c r="L13" s="26"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="20" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E14" s="21">
         <f>IF(D14="?OLD","!!!","")</f>
@@ -2516,16 +2499,7 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E15" s="21">
         <f>IF(D15="?OLD","!!!","")</f>
@@ -2559,7 +2533,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="20" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E16" s="21">
         <f>IF(D16="?OLD","!!!","")</f>
@@ -2593,16 +2567,16 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="20" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E17" s="21">
         <f>IF(D17="?OLD","!!!","")</f>
@@ -2636,7 +2610,7 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" s="21">
         <f>IF(D18="?OLD","!!!","")</f>
@@ -2670,13 +2644,16 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="C19" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>112</v>
+      <c r="D19" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E19" s="21">
         <f>IF(D19="?OLD","!!!","")</f>
@@ -2710,7 +2687,7 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E20" s="21">
         <f>IF(D20="?OLD","!!!","")</f>
@@ -2744,16 +2721,13 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="20" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B21" s="27" t="s">
         <v>114</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E21" s="21">
         <f>IF(D21="?OLD","!!!","")</f>
@@ -2787,7 +2761,7 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="20" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E22" s="21">
         <f>IF(D22="?OLD","!!!","")</f>
@@ -2821,7 +2795,16 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23" s="20" t="s">
-        <v>115</v>
+        <v>100</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E23" s="21">
         <f>IF(D23="?OLD","!!!","")</f>
@@ -2855,7 +2838,7 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" s="20" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="E24" s="21">
         <f>IF(D24="?OLD","!!!","")</f>
@@ -2889,7 +2872,7 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" s="20" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E25" s="21">
         <f>IF(D25="?OLD","!!!","")</f>
@@ -2923,7 +2906,7 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" s="20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E26" s="21">
         <f>IF(D26="?OLD","!!!","")</f>
@@ -2957,7 +2940,7 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="20" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E27" s="21">
         <f>IF(D27="?OLD","!!!","")</f>
@@ -2991,7 +2974,7 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E28" s="21">
         <f>IF(D28="?OLD","!!!","")</f>
@@ -3025,16 +3008,7 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E29" s="21">
         <f>IF(D29="?OLD","!!!","")</f>
@@ -3104,6 +3078,15 @@
       <c r="A31" s="20" t="s">
         <v>122</v>
       </c>
+      <c r="B31" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>98</v>
+      </c>
       <c r="E31" s="21">
         <f>IF(D31="?OLD","!!!","")</f>
         <v/>
@@ -3136,13 +3119,7 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E32" s="21">
         <f>IF(D32="?OLD","!!!","")</f>
@@ -3176,7 +3153,7 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="20" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E33" s="21">
         <f>IF(D33="?OLD","!!!","")</f>
@@ -3210,7 +3187,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="20" t="s">
-        <v>102</v>
+        <v>127</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>128</v>
       </c>
       <c r="E34" s="21">
         <f>IF(D34="?OLD","!!!","")</f>
@@ -3244,7 +3227,7 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="20" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E35" s="21">
         <f>IF(D35="?OLD","!!!","")</f>
@@ -3277,11 +3260,42 @@
       <c r="L35" s="26"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="20"/>
+      <c r="A36" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" s="21">
+        <f>IF(D36="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F36" s="22" t="str">
+        <f>IF(OR(E36="",E36="!!!"),"",IF(NOT(ISNA(VLOOKUP(E36,E$1:E35,1,FALSE()))),"OLD",IF(AND(E36&lt;&gt;"",E36&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G36" s="23" t="str">
+        <f>IF(OR(E36="",E36="!!!"),"",IF(OR(J36=0,AND(J36=1,K36=1),AND(J36=1,I36="SBJ"),AND(J36=1,I36=0)),"?IN_FOCUS",IF(J36&lt;=2,"?ACTIVATED",IF(J36&lt;&gt;"","?FAMILIAR",IF(F36="NEW",IF(ISNA(VLOOKUP(E36,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H36" s="24" t="str">
+        <f>IF(J36&lt;&gt;1,"",IF(I36="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I36" s="25" t="str">
+        <f>IF(OR(E36="",E36="!!!",F36="NEW"),"",INDEX(B35:B$2,-1+SUMPRODUCT(MAX(ROW(E35:E$2)*(E36=E35:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J36" s="25" t="str">
+        <f>IF(OR(E36="",E36="!!!",F36="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E36)*(E36=E$2:E36)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E35)*(E2=E$1:E35))))))</f>
+        <v> </v>
+      </c>
+      <c r="K36" s="25" t="str">
+        <f>IF(OR(E36="",E36="!!!",F36="NEW"),"",INDEX(J$1:J35,SUMPRODUCT(MAX(ROW(E$1:E35)*(E36=E$1:E35)))))</f>
+        <v> </v>
+      </c>
+      <c r="L36" s="26"/>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E37" s="21">
         <f>IF(D37="?OLD","!!!","")</f>
@@ -3314,13 +3328,11 @@
       <c r="L37" s="26"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="20" t="s">
-        <v>127</v>
-      </c>
+      <c r="A38" s="20"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="20" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E39" s="21">
         <f>IF(D39="?OLD","!!!","")</f>
@@ -3354,50 +3366,12 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E40" s="21">
-        <f>IF(D40="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F40" s="22" t="str">
-        <f>IF(OR(E40="",E40="!!!"),"",IF(NOT(ISNA(VLOOKUP(E40,E$1:E39,1,FALSE()))),"OLD",IF(AND(E40&lt;&gt;"",E40&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G40" s="23" t="str">
-        <f>IF(OR(E40="",E40="!!!"),"",IF(OR(J40=0,AND(J40=1,K40=1),AND(J40=1,I40="SBJ"),AND(J40=1,I40=0)),"?IN_FOCUS",IF(J40&lt;=2,"?ACTIVATED",IF(J40&lt;&gt;"","?FAMILIAR",IF(F40="NEW",IF(ISNA(VLOOKUP(E40,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H40" s="24" t="str">
-        <f>IF(J40&lt;&gt;1,"",IF(I40="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I40" s="25" t="str">
-        <f>IF(OR(E40="",E40="!!!",F40="NEW"),"",INDEX(B39:B$2,-1+SUMPRODUCT(MAX(ROW(E39:E$2)*(E40=E39:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J40" s="25" t="str">
-        <f>IF(OR(E40="",E40="!!!",F40="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E40)*(E40=E$2:E40)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E39)*(E2=E$1:E39))))))</f>
-        <v> </v>
-      </c>
-      <c r="K40" s="25" t="str">
-        <f>IF(OR(E40="",E40="!!!",F40="NEW"),"",INDEX(J$1:J39,SUMPRODUCT(MAX(ROW(E$1:E39)*(E40=E$1:E39)))))</f>
-        <v> </v>
-      </c>
-      <c r="L40" s="26"/>
+        <v>131</v>
+      </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E41" s="21">
         <f>IF(D41="?OLD","!!!","")</f>
@@ -3431,16 +3405,16 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B42" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C42" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D42" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E42" s="21">
         <f>IF(D42="?OLD","!!!","")</f>
@@ -3474,7 +3448,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="20" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E43" s="21">
         <f>IF(D43="?OLD","!!!","")</f>
@@ -3508,7 +3482,16 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" s="20" t="s">
-        <v>133</v>
+        <v>135</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E44" s="21">
         <f>IF(D44="?OLD","!!!","")</f>
@@ -3542,7 +3525,7 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" s="20" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="E45" s="21">
         <f>IF(D45="?OLD","!!!","")</f>
@@ -3576,7 +3559,7 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" s="20" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E46" s="21">
         <f>IF(D46="?OLD","!!!","")</f>
@@ -3610,16 +3593,7 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B47" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C47" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E47" s="21">
         <f>IF(D47="?OLD","!!!","")</f>
@@ -3655,9 +3629,6 @@
       <c r="A48" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="27" t="s">
-        <v>139</v>
-      </c>
       <c r="E48" s="21">
         <f>IF(D48="?OLD","!!!","")</f>
         <v/>
@@ -3690,13 +3661,16 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="27" t="s">
         <v>140</v>
-      </c>
-      <c r="B49" s="27" t="s">
-        <v>139</v>
       </c>
       <c r="C49" s="27" t="s">
         <v>141</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E49" s="21">
         <f>IF(D49="?OLD","!!!","")</f>
@@ -3732,6 +3706,9 @@
       <c r="A50" s="20" t="s">
         <v>142</v>
       </c>
+      <c r="B50" s="27" t="s">
+        <v>143</v>
+      </c>
       <c r="E50" s="21">
         <f>IF(D50="?OLD","!!!","")</f>
         <v/>
@@ -3764,7 +3741,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="27" t="s">
         <v>143</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="E51" s="21">
         <f>IF(D51="?OLD","!!!","")</f>
@@ -3798,7 +3781,7 @@
     </row>
     <row r="52" spans="1:12">
       <c r="A52" s="20" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="E52" s="21">
         <f>IF(D52="?OLD","!!!","")</f>
@@ -3832,10 +3815,7 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="27" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="E53" s="21">
         <f>IF(D53="?OLD","!!!","")</f>
@@ -3869,16 +3849,7 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="B54" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D54" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E54" s="21">
         <f>IF(D54="?OLD","!!!","")</f>
@@ -3912,7 +3883,10 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" s="20" t="s">
-        <v>145</v>
+        <v>109</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>140</v>
       </c>
       <c r="E55" s="21">
         <f>IF(D55="?OLD","!!!","")</f>
@@ -3946,7 +3920,16 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="20" t="s">
-        <v>146</v>
+        <v>148</v>
+      </c>
+      <c r="B56" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C56" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E56" s="21">
         <f>IF(D56="?OLD","!!!","")</f>
@@ -3980,7 +3963,7 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" s="20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E57" s="21">
         <f>IF(D57="?OLD","!!!","")</f>
@@ -4014,7 +3997,7 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" s="20" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="E58" s="21">
         <f>IF(D58="?OLD","!!!","")</f>
@@ -4048,7 +4031,7 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" s="20" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E59" s="21">
         <f>IF(D59="?OLD","!!!","")</f>
@@ -4082,7 +4065,7 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" s="20" t="s">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="E60" s="21">
         <f>IF(D60="?OLD","!!!","")</f>
@@ -4116,7 +4099,7 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" s="20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E61" s="21">
         <f>IF(D61="?OLD","!!!","")</f>
@@ -4150,16 +4133,7 @@
     </row>
     <row r="62" spans="1:12">
       <c r="A62" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D62" s="27" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="E62" s="21">
         <f>IF(D62="?OLD","!!!","")</f>
@@ -4193,7 +4167,7 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" s="20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E63" s="21">
         <f>IF(D63="?OLD","!!!","")</f>
@@ -4227,16 +4201,16 @@
     </row>
     <row r="64" spans="1:12">
       <c r="A64" s="20" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B64" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C64" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E64" s="21">
         <f>IF(D64="?OLD","!!!","")</f>
@@ -4270,7 +4244,7 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" s="20" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E65" s="21">
         <f>IF(D65="?OLD","!!!","")</f>
@@ -4304,7 +4278,16 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="20" t="s">
-        <v>154</v>
+        <v>148</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E66" s="21">
         <f>IF(D66="?OLD","!!!","")</f>
@@ -4338,7 +4321,7 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="20" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="E67" s="21">
         <f>IF(D67="?OLD","!!!","")</f>
@@ -4372,7 +4355,7 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="20" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E68" s="21">
         <f>IF(D68="?OLD","!!!","")</f>
@@ -4405,84 +4388,84 @@
       <c r="L68" s="26"/>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="20"/>
+      <c r="A69" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E69" s="21">
+        <f>IF(D69="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F69" s="22" t="str">
+        <f>IF(OR(E69="",E69="!!!"),"",IF(NOT(ISNA(VLOOKUP(E69,E$1:E68,1,FALSE()))),"OLD",IF(AND(E69&lt;&gt;"",E69&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G69" s="23" t="str">
+        <f>IF(OR(E69="",E69="!!!"),"",IF(OR(J69=0,AND(J69=1,K69=1),AND(J69=1,I69="SBJ"),AND(J69=1,I69=0)),"?IN_FOCUS",IF(J69&lt;=2,"?ACTIVATED",IF(J69&lt;&gt;"","?FAMILIAR",IF(F69="NEW",IF(ISNA(VLOOKUP(E69,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H69" s="24" t="str">
+        <f>IF(J69&lt;&gt;1,"",IF(I69="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I69" s="25" t="str">
+        <f>IF(OR(E69="",E69="!!!",F69="NEW"),"",INDEX(B68:B$2,-1+SUMPRODUCT(MAX(ROW(E68:E$2)*(E69=E68:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J69" s="25" t="str">
+        <f>IF(OR(E69="",E69="!!!",F69="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E69)*(E69=E$2:E69)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E68)*(E2=E$1:E68))))))</f>
+        <v> </v>
+      </c>
+      <c r="K69" s="25" t="str">
+        <f>IF(OR(E69="",E69="!!!",F69="NEW"),"",INDEX(J$1:J68,SUMPRODUCT(MAX(ROW(E$1:E68)*(E69=E$1:E68)))))</f>
+        <v> </v>
+      </c>
+      <c r="L69" s="26"/>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" s="20" t="s">
-        <v>155</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="E70" s="21">
+        <f>IF(D70="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F70" s="22" t="str">
+        <f>IF(OR(E70="",E70="!!!"),"",IF(NOT(ISNA(VLOOKUP(E70,E$1:E69,1,FALSE()))),"OLD",IF(AND(E70&lt;&gt;"",E70&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G70" s="23" t="str">
+        <f>IF(OR(E70="",E70="!!!"),"",IF(OR(J70=0,AND(J70=1,K70=1),AND(J70=1,I70="SBJ"),AND(J70=1,I70=0)),"?IN_FOCUS",IF(J70&lt;=2,"?ACTIVATED",IF(J70&lt;&gt;"","?FAMILIAR",IF(F70="NEW",IF(ISNA(VLOOKUP(E70,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H70" s="24" t="str">
+        <f>IF(J70&lt;&gt;1,"",IF(I70="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I70" s="25" t="str">
+        <f>IF(OR(E70="",E70="!!!",F70="NEW"),"",INDEX(B69:B$2,-1+SUMPRODUCT(MAX(ROW(E69:E$2)*(E70=E69:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J70" s="25" t="str">
+        <f>IF(OR(E70="",E70="!!!",F70="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E70)*(E70=E$2:E70)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E69)*(E2=E$1:E69))))))</f>
+        <v> </v>
+      </c>
+      <c r="K70" s="25" t="str">
+        <f>IF(OR(E70="",E70="!!!",F70="NEW"),"",INDEX(J$1:J69,SUMPRODUCT(MAX(ROW(E$1:E69)*(E70=E$1:E69)))))</f>
+        <v> </v>
+      </c>
+      <c r="L70" s="26"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E71" s="21">
-        <f>IF(D71="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F71" s="22" t="str">
-        <f>IF(OR(E71="",E71="!!!"),"",IF(NOT(ISNA(VLOOKUP(E71,E$1:E70,1,FALSE()))),"OLD",IF(AND(E71&lt;&gt;"",E71&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G71" s="23" t="str">
-        <f>IF(OR(E71="",E71="!!!"),"",IF(OR(J71=0,AND(J71=1,K71=1),AND(J71=1,I71="SBJ"),AND(J71=1,I71=0)),"?IN_FOCUS",IF(J71&lt;=2,"?ACTIVATED",IF(J71&lt;&gt;"","?FAMILIAR",IF(F71="NEW",IF(ISNA(VLOOKUP(E71,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H71" s="24" t="str">
-        <f>IF(J71&lt;&gt;1,"",IF(I71="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I71" s="25" t="str">
-        <f>IF(OR(E71="",E71="!!!",F71="NEW"),"",INDEX(B70:B$2,-1+SUMPRODUCT(MAX(ROW(E70:E$2)*(E71=E70:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J71" s="25" t="str">
-        <f>IF(OR(E71="",E71="!!!",F71="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E71)*(E71=E$2:E71)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E70)*(E2=E$1:E70))))))</f>
-        <v> </v>
-      </c>
-      <c r="K71" s="25" t="str">
-        <f>IF(OR(E71="",E71="!!!",F71="NEW"),"",INDEX(J$1:J70,SUMPRODUCT(MAX(ROW(E$1:E70)*(E71=E$1:E70)))))</f>
-        <v> </v>
-      </c>
-      <c r="L71" s="26"/>
+      <c r="A71" s="20"/>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="E72" s="21">
-        <f>IF(D72="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F72" s="22" t="str">
-        <f>IF(OR(E72="",E72="!!!"),"",IF(NOT(ISNA(VLOOKUP(E72,E$1:E71,1,FALSE()))),"OLD",IF(AND(E72&lt;&gt;"",E72&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G72" s="23" t="str">
-        <f>IF(OR(E72="",E72="!!!"),"",IF(OR(J72=0,AND(J72=1,K72=1),AND(J72=1,I72="SBJ"),AND(J72=1,I72=0)),"?IN_FOCUS",IF(J72&lt;=2,"?ACTIVATED",IF(J72&lt;&gt;"","?FAMILIAR",IF(F72="NEW",IF(ISNA(VLOOKUP(E72,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H72" s="24" t="str">
-        <f>IF(J72&lt;&gt;1,"",IF(I72="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I72" s="25" t="str">
-        <f>IF(OR(E72="",E72="!!!",F72="NEW"),"",INDEX(B71:B$2,-1+SUMPRODUCT(MAX(ROW(E71:E$2)*(E72=E71:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J72" s="25" t="str">
-        <f>IF(OR(E72="",E72="!!!",F72="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E72)*(E72=E$2:E72)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E71)*(E2=E$1:E71))))))</f>
-        <v> </v>
-      </c>
-      <c r="K72" s="25" t="str">
-        <f>IF(OR(E72="",E72="!!!",F72="NEW"),"",INDEX(J$1:J71,SUMPRODUCT(MAX(ROW(E$1:E71)*(E72=E$1:E71)))))</f>
-        <v> </v>
-      </c>
-      <c r="L72" s="26"/>
+        <v>159</v>
+      </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="20" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E73" s="21">
         <f>IF(D73="?OLD","!!!","")</f>
@@ -4516,16 +4499,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="B74" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C74" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="E74" s="21">
         <f>IF(D74="?OLD","!!!","")</f>
@@ -4559,7 +4533,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" s="20" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="E75" s="21">
         <f>IF(D75="?OLD","!!!","")</f>
@@ -4593,7 +4567,16 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="20" t="s">
-        <v>96</v>
+        <v>161</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E76" s="21">
         <f>IF(D76="?OLD","!!!","")</f>
@@ -4627,7 +4610,7 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="20" t="s">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="E77" s="21">
         <f>IF(D77="?OLD","!!!","")</f>
@@ -4661,16 +4644,7 @@
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="B78" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C78" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D78" s="27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E78" s="21">
         <f>IF(D78="?OLD","!!!","")</f>
@@ -4704,7 +4678,7 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="20" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="E79" s="21">
         <f>IF(D79="?OLD","!!!","")</f>
@@ -4738,7 +4712,16 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="20" t="s">
-        <v>160</v>
+        <v>163</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C80" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D80" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E80" s="21">
         <f>IF(D80="?OLD","!!!","")</f>
@@ -4772,16 +4755,7 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
-        <v>161</v>
-      </c>
-      <c r="B81" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C81" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D81" s="27" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E81" s="21">
         <f>IF(D81="?OLD","!!!","")</f>
@@ -4815,7 +4789,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="20" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="E82" s="21">
         <f>IF(D82="?OLD","!!!","")</f>
@@ -4849,7 +4823,16 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
-        <v>162</v>
+        <v>165</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E83" s="21">
         <f>IF(D83="?OLD","!!!","")</f>
@@ -4883,7 +4866,7 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" s="20" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E84" s="21">
         <f>IF(D84="?OLD","!!!","")</f>
@@ -4917,7 +4900,7 @@
     </row>
     <row r="85" spans="1:12">
       <c r="A85" s="20" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E85" s="21">
         <f>IF(D85="?OLD","!!!","")</f>
@@ -4951,13 +4934,7 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="B86" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C86" s="27" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="E86" s="21">
         <f>IF(D86="?OLD","!!!","")</f>
@@ -4991,7 +4968,7 @@
     </row>
     <row r="87" spans="1:12">
       <c r="A87" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E87" s="21">
         <f>IF(D87="?OLD","!!!","")</f>
@@ -5025,16 +5002,13 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="C88" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D88" s="27" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="E88" s="21">
         <f>IF(D88="?OLD","!!!","")</f>
@@ -5068,7 +5042,7 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E89" s="21">
         <f>IF(D89="?OLD","!!!","")</f>
@@ -5102,7 +5076,16 @@
     </row>
     <row r="90" spans="1:12">
       <c r="A90" s="20" t="s">
-        <v>133</v>
+        <v>171</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C90" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E90" s="21">
         <f>IF(D90="?OLD","!!!","")</f>
@@ -5136,16 +5119,7 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C91" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D91" s="27" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="E91" s="21">
         <f>IF(D91="?OLD","!!!","")</f>
@@ -5179,7 +5153,7 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" s="20" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="E92" s="21">
         <f>IF(D92="?OLD","!!!","")</f>
@@ -5213,7 +5187,16 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" s="20" t="s">
-        <v>170</v>
+        <v>100</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C93" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D93" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E93" s="21">
         <f>IF(D93="?OLD","!!!","")</f>
@@ -5247,7 +5230,7 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" s="20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E94" s="21">
         <f>IF(D94="?OLD","!!!","")</f>
@@ -5281,7 +5264,7 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" s="20" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E95" s="21">
         <f>IF(D95="?OLD","!!!","")</f>
@@ -5315,7 +5298,7 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" s="20" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="E96" s="21">
         <f>IF(D96="?OLD","!!!","")</f>
@@ -5349,7 +5332,7 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E97" s="21">
         <f>IF(D97="?OLD","!!!","")</f>
@@ -5383,16 +5366,7 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="B98" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D98" s="27" t="s">
-        <v>95</v>
+        <v>175</v>
       </c>
       <c r="E98" s="21">
         <f>IF(D98="?OLD","!!!","")</f>
@@ -5426,7 +5400,7 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" s="20" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="E99" s="21">
         <f>IF(D99="?OLD","!!!","")</f>
@@ -5460,16 +5434,16 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" s="20" t="s">
-        <v>97</v>
+        <v>177</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E100" s="21">
         <f>IF(D100="?OLD","!!!","")</f>
@@ -5537,7 +5511,16 @@
     </row>
     <row r="102" spans="1:12">
       <c r="A102" s="20" t="s">
-        <v>175</v>
+        <v>100</v>
+      </c>
+      <c r="B102" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C102" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D102" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E102" s="21">
         <f>IF(D102="?OLD","!!!","")</f>
@@ -5571,7 +5554,7 @@
     </row>
     <row r="103" spans="1:12">
       <c r="A103" s="20" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E103" s="21">
         <f>IF(D103="?OLD","!!!","")</f>
@@ -5604,93 +5587,84 @@
       <c r="L103" s="26"/>
     </row>
     <row r="104" spans="1:12">
-      <c r="A104" s="20"/>
+      <c r="A104" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E104" s="21">
+        <f>IF(D104="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F104" s="22" t="str">
+        <f>IF(OR(E104="",E104="!!!"),"",IF(NOT(ISNA(VLOOKUP(E104,E$1:E103,1,FALSE()))),"OLD",IF(AND(E104&lt;&gt;"",E104&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G104" s="23" t="str">
+        <f>IF(OR(E104="",E104="!!!"),"",IF(OR(J104=0,AND(J104=1,K104=1),AND(J104=1,I104="SBJ"),AND(J104=1,I104=0)),"?IN_FOCUS",IF(J104&lt;=2,"?ACTIVATED",IF(J104&lt;&gt;"","?FAMILIAR",IF(F104="NEW",IF(ISNA(VLOOKUP(E104,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H104" s="24" t="str">
+        <f>IF(J104&lt;&gt;1,"",IF(I104="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I104" s="25" t="str">
+        <f>IF(OR(E104="",E104="!!!",F104="NEW"),"",INDEX(B103:B$2,-1+SUMPRODUCT(MAX(ROW(E103:E$2)*(E104=E103:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J104" s="25" t="str">
+        <f>IF(OR(E104="",E104="!!!",F104="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E104)*(E104=E$2:E104)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E103)*(E2=E$1:E103))))))</f>
+        <v> </v>
+      </c>
+      <c r="K104" s="25" t="str">
+        <f>IF(OR(E104="",E104="!!!",F104="NEW"),"",INDEX(J$1:J103,SUMPRODUCT(MAX(ROW(E$1:E103)*(E104=E$1:E103)))))</f>
+        <v> </v>
+      </c>
+      <c r="L104" s="26"/>
     </row>
     <row r="105" spans="1:12">
       <c r="A105" s="20" t="s">
-        <v>176</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E105" s="21">
+        <f>IF(D105="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F105" s="22" t="str">
+        <f>IF(OR(E105="",E105="!!!"),"",IF(NOT(ISNA(VLOOKUP(E105,E$1:E104,1,FALSE()))),"OLD",IF(AND(E105&lt;&gt;"",E105&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G105" s="23" t="str">
+        <f>IF(OR(E105="",E105="!!!"),"",IF(OR(J105=0,AND(J105=1,K105=1),AND(J105=1,I105="SBJ"),AND(J105=1,I105=0)),"?IN_FOCUS",IF(J105&lt;=2,"?ACTIVATED",IF(J105&lt;&gt;"","?FAMILIAR",IF(F105="NEW",IF(ISNA(VLOOKUP(E105,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H105" s="24" t="str">
+        <f>IF(J105&lt;&gt;1,"",IF(I105="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I105" s="25" t="str">
+        <f>IF(OR(E105="",E105="!!!",F105="NEW"),"",INDEX(B104:B$2,-1+SUMPRODUCT(MAX(ROW(E104:E$2)*(E105=E104:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J105" s="25" t="str">
+        <f>IF(OR(E105="",E105="!!!",F105="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E105)*(E105=E$2:E105)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E104)*(E2=E$1:E104))))))</f>
+        <v> </v>
+      </c>
+      <c r="K105" s="25" t="str">
+        <f>IF(OR(E105="",E105="!!!",F105="NEW"),"",INDEX(J$1:J104,SUMPRODUCT(MAX(ROW(E$1:E104)*(E105=E$1:E104)))))</f>
+        <v> </v>
+      </c>
+      <c r="L105" s="26"/>
     </row>
     <row r="106" spans="1:12">
-      <c r="A106" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="E106" s="21">
-        <f>IF(D106="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F106" s="22" t="str">
-        <f>IF(OR(E106="",E106="!!!"),"",IF(NOT(ISNA(VLOOKUP(E106,E$1:E105,1,FALSE()))),"OLD",IF(AND(E106&lt;&gt;"",E106&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G106" s="23" t="str">
-        <f>IF(OR(E106="",E106="!!!"),"",IF(OR(J106=0,AND(J106=1,K106=1),AND(J106=1,I106="SBJ"),AND(J106=1,I106=0)),"?IN_FOCUS",IF(J106&lt;=2,"?ACTIVATED",IF(J106&lt;&gt;"","?FAMILIAR",IF(F106="NEW",IF(ISNA(VLOOKUP(E106,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H106" s="24" t="str">
-        <f>IF(J106&lt;&gt;1,"",IF(I106="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I106" s="25" t="str">
-        <f>IF(OR(E106="",E106="!!!",F106="NEW"),"",INDEX(B105:B$2,-1+SUMPRODUCT(MAX(ROW(E105:E$2)*(E106=E105:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J106" s="25" t="str">
-        <f>IF(OR(E106="",E106="!!!",F106="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E106)*(E106=E$2:E106)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E105)*(E2=E$1:E105))))))</f>
-        <v> </v>
-      </c>
-      <c r="K106" s="25" t="str">
-        <f>IF(OR(E106="",E106="!!!",F106="NEW"),"",INDEX(J$1:J105,SUMPRODUCT(MAX(ROW(E$1:E105)*(E106=E$1:E105)))))</f>
-        <v> </v>
-      </c>
-      <c r="L106" s="26"/>
+      <c r="A106" s="20"/>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B107" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C107" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D107" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E107" s="21">
-        <f>IF(D107="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F107" s="22" t="str">
-        <f>IF(OR(E107="",E107="!!!"),"",IF(NOT(ISNA(VLOOKUP(E107,E$1:E106,1,FALSE()))),"OLD",IF(AND(E107&lt;&gt;"",E107&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G107" s="23" t="str">
-        <f>IF(OR(E107="",E107="!!!"),"",IF(OR(J107=0,AND(J107=1,K107=1),AND(J107=1,I107="SBJ"),AND(J107=1,I107=0)),"?IN_FOCUS",IF(J107&lt;=2,"?ACTIVATED",IF(J107&lt;&gt;"","?FAMILIAR",IF(F107="NEW",IF(ISNA(VLOOKUP(E107,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H107" s="24" t="str">
-        <f>IF(J107&lt;&gt;1,"",IF(I107="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I107" s="25" t="str">
-        <f>IF(OR(E107="",E107="!!!",F107="NEW"),"",INDEX(B106:B$2,-1+SUMPRODUCT(MAX(ROW(E106:E$2)*(E107=E106:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J107" s="25" t="str">
-        <f>IF(OR(E107="",E107="!!!",F107="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E107)*(E107=E$2:E107)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E106)*(E2=E$1:E106))))))</f>
-        <v> </v>
-      </c>
-      <c r="K107" s="25" t="str">
-        <f>IF(OR(E107="",E107="!!!",F107="NEW"),"",INDEX(J$1:J106,SUMPRODUCT(MAX(ROW(E$1:E106)*(E107=E$1:E106)))))</f>
-        <v> </v>
-      </c>
-      <c r="L107" s="26"/>
+        <v>179</v>
+      </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" s="20" t="s">
-        <v>99</v>
+        <v>180</v>
       </c>
       <c r="E108" s="21">
         <f>IF(D108="?OLD","!!!","")</f>
@@ -5724,7 +5698,16 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" s="20" t="s">
-        <v>178</v>
+        <v>100</v>
+      </c>
+      <c r="B109" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C109" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D109" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E109" s="21">
         <f>IF(D109="?OLD","!!!","")</f>
@@ -5758,7 +5741,7 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" s="20" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="E110" s="21">
         <f>IF(D110="?OLD","!!!","")</f>
@@ -5792,7 +5775,7 @@
     </row>
     <row r="111" spans="1:12">
       <c r="A111" s="20" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="E111" s="21">
         <f>IF(D111="?OLD","!!!","")</f>
@@ -5826,7 +5809,7 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" s="20" t="s">
-        <v>105</v>
+        <v>182</v>
       </c>
       <c r="E112" s="21">
         <f>IF(D112="?OLD","!!!","")</f>
@@ -5860,7 +5843,7 @@
     </row>
     <row r="113" spans="1:12">
       <c r="A113" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E113" s="21">
         <f>IF(D113="?OLD","!!!","")</f>
@@ -5894,7 +5877,7 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E114" s="21">
         <f>IF(D114="?OLD","!!!","")</f>
@@ -5928,16 +5911,7 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B115" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C115" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D115" s="27" t="s">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="E115" s="21">
         <f>IF(D115="?OLD","!!!","")</f>
@@ -5971,7 +5945,7 @@
     </row>
     <row r="116" spans="1:12">
       <c r="A116" s="20" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="E116" s="21">
         <f>IF(D116="?OLD","!!!","")</f>
@@ -6005,13 +5979,16 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" s="20" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B117" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C117" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D117" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C117" s="27" t="s">
-        <v>112</v>
       </c>
       <c r="E117" s="21">
         <f>IF(D117="?OLD","!!!","")</f>
@@ -6045,7 +6022,7 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" s="20" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E118" s="21">
         <f>IF(D118="?OLD","!!!","")</f>
@@ -6079,7 +6056,13 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" s="20" t="s">
-        <v>117</v>
+        <v>184</v>
+      </c>
+      <c r="B119" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C119" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="E119" s="21">
         <f>IF(D119="?OLD","!!!","")</f>
@@ -6113,7 +6096,7 @@
     </row>
     <row r="120" spans="1:12">
       <c r="A120" s="20" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E120" s="21">
         <f>IF(D120="?OLD","!!!","")</f>
@@ -6147,7 +6130,7 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" s="20" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="E121" s="21">
         <f>IF(D121="?OLD","!!!","")</f>
@@ -6181,16 +6164,7 @@
     </row>
     <row r="122" spans="1:12">
       <c r="A122" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="B122" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C122" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D122" s="27" t="s">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="E122" s="21">
         <f>IF(D122="?OLD","!!!","")</f>
@@ -6224,7 +6198,7 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" s="20" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="E123" s="21">
         <f>IF(D123="?OLD","!!!","")</f>
@@ -6258,7 +6232,16 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" s="20" t="s">
-        <v>118</v>
+        <v>187</v>
+      </c>
+      <c r="B124" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C124" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D124" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E124" s="21">
         <f>IF(D124="?OLD","!!!","")</f>
@@ -6292,16 +6275,7 @@
     </row>
     <row r="125" spans="1:12">
       <c r="A125" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="B125" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C125" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D125" s="27" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="E125" s="21">
         <f>IF(D125="?OLD","!!!","")</f>
@@ -6335,7 +6309,7 @@
     </row>
     <row r="126" spans="1:12">
       <c r="A126" s="20" t="s">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="E126" s="21">
         <f>IF(D126="?OLD","!!!","")</f>
@@ -6369,7 +6343,16 @@
     </row>
     <row r="127" spans="1:12">
       <c r="A127" s="20" t="s">
-        <v>125</v>
+        <v>188</v>
+      </c>
+      <c r="B127" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D127" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E127" s="21">
         <f>IF(D127="?OLD","!!!","")</f>
@@ -6402,93 +6385,84 @@
       <c r="L127" s="26"/>
     </row>
     <row r="128" spans="1:12">
-      <c r="A128" s="20"/>
+      <c r="A128" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E128" s="21">
+        <f>IF(D128="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F128" s="22" t="str">
+        <f>IF(OR(E128="",E128="!!!"),"",IF(NOT(ISNA(VLOOKUP(E128,E$1:E127,1,FALSE()))),"OLD",IF(AND(E128&lt;&gt;"",E128&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G128" s="23" t="str">
+        <f>IF(OR(E128="",E128="!!!"),"",IF(OR(J128=0,AND(J128=1,K128=1),AND(J128=1,I128="SBJ"),AND(J128=1,I128=0)),"?IN_FOCUS",IF(J128&lt;=2,"?ACTIVATED",IF(J128&lt;&gt;"","?FAMILIAR",IF(F128="NEW",IF(ISNA(VLOOKUP(E128,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H128" s="24" t="str">
+        <f>IF(J128&lt;&gt;1,"",IF(I128="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I128" s="25" t="str">
+        <f>IF(OR(E128="",E128="!!!",F128="NEW"),"",INDEX(B127:B$2,-1+SUMPRODUCT(MAX(ROW(E127:E$2)*(E128=E127:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J128" s="25" t="str">
+        <f>IF(OR(E128="",E128="!!!",F128="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E128)*(E128=E$2:E128)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E127)*(E2=E$1:E127))))))</f>
+        <v> </v>
+      </c>
+      <c r="K128" s="25" t="str">
+        <f>IF(OR(E128="",E128="!!!",F128="NEW"),"",INDEX(J$1:J127,SUMPRODUCT(MAX(ROW(E$1:E127)*(E128=E$1:E127)))))</f>
+        <v> </v>
+      </c>
+      <c r="L128" s="26"/>
     </row>
     <row r="129" spans="1:12">
       <c r="A129" s="20" t="s">
-        <v>187</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E129" s="21">
+        <f>IF(D129="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F129" s="22" t="str">
+        <f>IF(OR(E129="",E129="!!!"),"",IF(NOT(ISNA(VLOOKUP(E129,E$1:E128,1,FALSE()))),"OLD",IF(AND(E129&lt;&gt;"",E129&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G129" s="23" t="str">
+        <f>IF(OR(E129="",E129="!!!"),"",IF(OR(J129=0,AND(J129=1,K129=1),AND(J129=1,I129="SBJ"),AND(J129=1,I129=0)),"?IN_FOCUS",IF(J129&lt;=2,"?ACTIVATED",IF(J129&lt;&gt;"","?FAMILIAR",IF(F129="NEW",IF(ISNA(VLOOKUP(E129,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H129" s="24" t="str">
+        <f>IF(J129&lt;&gt;1,"",IF(I129="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I129" s="25" t="str">
+        <f>IF(OR(E129="",E129="!!!",F129="NEW"),"",INDEX(B128:B$2,-1+SUMPRODUCT(MAX(ROW(E128:E$2)*(E129=E128:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J129" s="25" t="str">
+        <f>IF(OR(E129="",E129="!!!",F129="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E129)*(E129=E$2:E129)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E128)*(E2=E$1:E128))))))</f>
+        <v> </v>
+      </c>
+      <c r="K129" s="25" t="str">
+        <f>IF(OR(E129="",E129="!!!",F129="NEW"),"",INDEX(J$1:J128,SUMPRODUCT(MAX(ROW(E$1:E128)*(E129=E$1:E128)))))</f>
+        <v> </v>
+      </c>
+      <c r="L129" s="26"/>
     </row>
     <row r="130" spans="1:12">
-      <c r="A130" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="E130" s="21">
-        <f>IF(D130="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F130" s="22" t="str">
-        <f>IF(OR(E130="",E130="!!!"),"",IF(NOT(ISNA(VLOOKUP(E130,E$1:E129,1,FALSE()))),"OLD",IF(AND(E130&lt;&gt;"",E130&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G130" s="23" t="str">
-        <f>IF(OR(E130="",E130="!!!"),"",IF(OR(J130=0,AND(J130=1,K130=1),AND(J130=1,I130="SBJ"),AND(J130=1,I130=0)),"?IN_FOCUS",IF(J130&lt;=2,"?ACTIVATED",IF(J130&lt;&gt;"","?FAMILIAR",IF(F130="NEW",IF(ISNA(VLOOKUP(E130,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H130" s="24" t="str">
-        <f>IF(J130&lt;&gt;1,"",IF(I130="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I130" s="25" t="str">
-        <f>IF(OR(E130="",E130="!!!",F130="NEW"),"",INDEX(B129:B$2,-1+SUMPRODUCT(MAX(ROW(E129:E$2)*(E130=E129:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J130" s="25" t="str">
-        <f>IF(OR(E130="",E130="!!!",F130="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E130)*(E130=E$2:E130)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E129)*(E2=E$1:E129))))))</f>
-        <v> </v>
-      </c>
-      <c r="K130" s="25" t="str">
-        <f>IF(OR(E130="",E130="!!!",F130="NEW"),"",INDEX(J$1:J129,SUMPRODUCT(MAX(ROW(E$1:E129)*(E130=E$1:E129)))))</f>
-        <v> </v>
-      </c>
-      <c r="L130" s="26"/>
+      <c r="A130" s="20"/>
     </row>
     <row r="131" spans="1:12">
       <c r="A131" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B131" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C131" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D131" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E131" s="21">
-        <f>IF(D131="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F131" s="22" t="str">
-        <f>IF(OR(E131="",E131="!!!"),"",IF(NOT(ISNA(VLOOKUP(E131,E$1:E130,1,FALSE()))),"OLD",IF(AND(E131&lt;&gt;"",E131&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G131" s="23" t="str">
-        <f>IF(OR(E131="",E131="!!!"),"",IF(OR(J131=0,AND(J131=1,K131=1),AND(J131=1,I131="SBJ"),AND(J131=1,I131=0)),"?IN_FOCUS",IF(J131&lt;=2,"?ACTIVATED",IF(J131&lt;&gt;"","?FAMILIAR",IF(F131="NEW",IF(ISNA(VLOOKUP(E131,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H131" s="24" t="str">
-        <f>IF(J131&lt;&gt;1,"",IF(I131="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I131" s="25" t="str">
-        <f>IF(OR(E131="",E131="!!!",F131="NEW"),"",INDEX(B130:B$2,-1+SUMPRODUCT(MAX(ROW(E130:E$2)*(E131=E130:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J131" s="25" t="str">
-        <f>IF(OR(E131="",E131="!!!",F131="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E131)*(E131=E$2:E131)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E130)*(E2=E$1:E130))))))</f>
-        <v> </v>
-      </c>
-      <c r="K131" s="25" t="str">
-        <f>IF(OR(E131="",E131="!!!",F131="NEW"),"",INDEX(J$1:J130,SUMPRODUCT(MAX(ROW(E$1:E130)*(E131=E$1:E130)))))</f>
-        <v> </v>
-      </c>
-      <c r="L131" s="26"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="132" spans="1:12">
       <c r="A132" s="20" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E132" s="21">
         <f>IF(D132="?OLD","!!!","")</f>
@@ -6522,16 +6496,16 @@
     </row>
     <row r="133" spans="1:12">
       <c r="A133" s="20" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B133" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C133" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D133" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C133" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D133" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E133" s="21">
         <f>IF(D133="?OLD","!!!","")</f>
@@ -6565,7 +6539,7 @@
     </row>
     <row r="134" spans="1:12">
       <c r="A134" s="20" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="E134" s="21">
         <f>IF(D134="?OLD","!!!","")</f>
@@ -6599,16 +6573,16 @@
     </row>
     <row r="135" spans="1:12">
       <c r="A135" s="20" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="B135" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C135" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D135" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C135" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D135" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E135" s="21">
         <f>IF(D135="?OLD","!!!","")</f>
@@ -6642,7 +6616,7 @@
     </row>
     <row r="136" spans="1:12">
       <c r="A136" s="20" t="s">
-        <v>169</v>
+        <v>108</v>
       </c>
       <c r="E136" s="21">
         <f>IF(D136="?OLD","!!!","")</f>
@@ -6676,7 +6650,16 @@
     </row>
     <row r="137" spans="1:12">
       <c r="A137" s="20" t="s">
-        <v>105</v>
+        <v>191</v>
+      </c>
+      <c r="B137" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C137" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D137" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E137" s="21">
         <f>IF(D137="?OLD","!!!","")</f>
@@ -6710,7 +6693,7 @@
     </row>
     <row r="138" spans="1:12">
       <c r="A138" s="20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E138" s="21">
         <f>IF(D138="?OLD","!!!","")</f>
@@ -6744,7 +6727,7 @@
     </row>
     <row r="139" spans="1:12">
       <c r="A139" s="20" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E139" s="21">
         <f>IF(D139="?OLD","!!!","")</f>
@@ -6778,16 +6761,7 @@
     </row>
     <row r="140" spans="1:12">
       <c r="A140" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="B140" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C140" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D140" s="27" t="s">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="E140" s="21">
         <f>IF(D140="?OLD","!!!","")</f>
@@ -6821,16 +6795,7 @@
     </row>
     <row r="141" spans="1:12">
       <c r="A141" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B141" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C141" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D141" s="27" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="E141" s="21">
         <f>IF(D141="?OLD","!!!","")</f>
@@ -6864,7 +6829,16 @@
     </row>
     <row r="142" spans="1:12">
       <c r="A142" s="20" t="s">
-        <v>191</v>
+        <v>192</v>
+      </c>
+      <c r="B142" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C142" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D142" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E142" s="21">
         <f>IF(D142="?OLD","!!!","")</f>
@@ -6898,7 +6872,16 @@
     </row>
     <row r="143" spans="1:12">
       <c r="A143" s="20" t="s">
-        <v>96</v>
+        <v>194</v>
+      </c>
+      <c r="B143" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C143" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D143" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E143" s="21">
         <f>IF(D143="?OLD","!!!","")</f>
@@ -6932,16 +6915,7 @@
     </row>
     <row r="144" spans="1:12">
       <c r="A144" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B144" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C144" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D144" s="27" t="s">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="E144" s="21">
         <f>IF(D144="?OLD","!!!","")</f>
@@ -7009,7 +6983,16 @@
     </row>
     <row r="146" spans="1:12">
       <c r="A146" s="20" t="s">
-        <v>175</v>
+        <v>100</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C146" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D146" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E146" s="21">
         <f>IF(D146="?OLD","!!!","")</f>
@@ -7043,7 +7026,7 @@
     </row>
     <row r="147" spans="1:12">
       <c r="A147" s="20" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E147" s="21">
         <f>IF(D147="?OLD","!!!","")</f>
@@ -7077,7 +7060,7 @@
     </row>
     <row r="148" spans="1:12">
       <c r="A148" s="20" t="s">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="E148" s="21">
         <f>IF(D148="?OLD","!!!","")</f>
@@ -7111,16 +7094,7 @@
     </row>
     <row r="149" spans="1:12">
       <c r="A149" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="B149" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C149" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D149" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E149" s="21">
         <f>IF(D149="?OLD","!!!","")</f>
@@ -7154,7 +7128,7 @@
     </row>
     <row r="150" spans="1:12">
       <c r="A150" s="20" t="s">
-        <v>105</v>
+        <v>138</v>
       </c>
       <c r="E150" s="21">
         <f>IF(D150="?OLD","!!!","")</f>
@@ -7188,10 +7162,16 @@
     </row>
     <row r="151" spans="1:12">
       <c r="A151" s="20" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="B151" s="27" t="s">
-        <v>192</v>
+        <v>140</v>
+      </c>
+      <c r="C151" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D151" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E151" s="21">
         <f>IF(D151="?OLD","!!!","")</f>
@@ -7225,7 +7205,7 @@
     </row>
     <row r="152" spans="1:12">
       <c r="A152" s="20" t="s">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="E152" s="21">
         <f>IF(D152="?OLD","!!!","")</f>
@@ -7259,7 +7239,10 @@
     </row>
     <row r="153" spans="1:12">
       <c r="A153" s="20" t="s">
-        <v>162</v>
+        <v>109</v>
+      </c>
+      <c r="B153" s="27" t="s">
+        <v>196</v>
       </c>
       <c r="E153" s="21">
         <f>IF(D153="?OLD","!!!","")</f>
@@ -7293,16 +7276,7 @@
     </row>
     <row r="154" spans="1:12">
       <c r="A154" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="B154" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C154" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D154" s="27" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="E154" s="21">
         <f>IF(D154="?OLD","!!!","")</f>
@@ -7336,7 +7310,7 @@
     </row>
     <row r="155" spans="1:12">
       <c r="A155" s="20" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="E155" s="21">
         <f>IF(D155="?OLD","!!!","")</f>
@@ -7370,16 +7344,16 @@
     </row>
     <row r="156" spans="1:12">
       <c r="A156" s="20" t="s">
-        <v>194</v>
+        <v>95</v>
       </c>
       <c r="B156" s="27" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C156" s="27" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D156" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E156" s="21">
         <f>IF(D156="?OLD","!!!","")</f>
@@ -7413,7 +7387,7 @@
     </row>
     <row r="157" spans="1:12">
       <c r="A157" s="20" t="s">
-        <v>195</v>
+        <v>99</v>
       </c>
       <c r="E157" s="21">
         <f>IF(D157="?OLD","!!!","")</f>
@@ -7447,7 +7421,16 @@
     </row>
     <row r="158" spans="1:12">
       <c r="A158" s="20" t="s">
-        <v>196</v>
+        <v>198</v>
+      </c>
+      <c r="B158" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C158" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D158" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E158" s="21">
         <f>IF(D158="?OLD","!!!","")</f>
@@ -7481,7 +7464,7 @@
     </row>
     <row r="159" spans="1:12">
       <c r="A159" s="20" t="s">
-        <v>105</v>
+        <v>199</v>
       </c>
       <c r="E159" s="21">
         <f>IF(D159="?OLD","!!!","")</f>
@@ -7515,7 +7498,7 @@
     </row>
     <row r="160" spans="1:12">
       <c r="A160" s="20" t="s">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="E160" s="21">
         <f>IF(D160="?OLD","!!!","")</f>
@@ -7549,7 +7532,7 @@
     </row>
     <row r="161" spans="1:12">
       <c r="A161" s="20" t="s">
-        <v>197</v>
+        <v>108</v>
       </c>
       <c r="E161" s="21">
         <f>IF(D161="?OLD","!!!","")</f>
@@ -7583,13 +7566,7 @@
     </row>
     <row r="162" spans="1:12">
       <c r="A162" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B162" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C162" s="27" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="E162" s="21">
         <f>IF(D162="?OLD","!!!","")</f>
@@ -7623,7 +7600,7 @@
     </row>
     <row r="163" spans="1:12">
       <c r="A163" s="20" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E163" s="21">
         <f>IF(D163="?OLD","!!!","")</f>
@@ -7657,13 +7634,13 @@
     </row>
     <row r="164" spans="1:12">
       <c r="A164" s="20" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B164" s="27" t="s">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="C164" s="27" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="E164" s="21">
         <f>IF(D164="?OLD","!!!","")</f>
@@ -7697,7 +7674,7 @@
     </row>
     <row r="165" spans="1:12">
       <c r="A165" s="20" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="E165" s="21">
         <f>IF(D165="?OLD","!!!","")</f>
@@ -7731,13 +7708,13 @@
     </row>
     <row r="166" spans="1:12">
       <c r="A166" s="20" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="B166" s="27" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
       <c r="C166" s="27" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="E166" s="21">
         <f>IF(D166="?OLD","!!!","")</f>
@@ -7771,7 +7748,7 @@
     </row>
     <row r="167" spans="1:12">
       <c r="A167" s="20" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="E167" s="21">
         <f>IF(D167="?OLD","!!!","")</f>
@@ -7805,7 +7782,13 @@
     </row>
     <row r="168" spans="1:12">
       <c r="A168" s="20" t="s">
-        <v>118</v>
+        <v>95</v>
+      </c>
+      <c r="B168" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C168" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="E168" s="21">
         <f>IF(D168="?OLD","!!!","")</f>
@@ -7839,16 +7822,7 @@
     </row>
     <row r="169" spans="1:12">
       <c r="A169" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="B169" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C169" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D169" s="27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E169" s="21">
         <f>IF(D169="?OLD","!!!","")</f>
@@ -7882,7 +7856,7 @@
     </row>
     <row r="170" spans="1:12">
       <c r="A170" s="20" t="s">
-        <v>203</v>
+        <v>121</v>
       </c>
       <c r="E170" s="21">
         <f>IF(D170="?OLD","!!!","")</f>
@@ -7916,16 +7890,16 @@
     </row>
     <row r="171" spans="1:12">
       <c r="A171" s="20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B171" s="27" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C171" s="27" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D171" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E171" s="21">
         <f>IF(D171="?OLD","!!!","")</f>
@@ -7959,13 +7933,7 @@
     </row>
     <row r="172" spans="1:12">
       <c r="A172" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="B172" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C172" s="27" t="s">
-        <v>112</v>
+        <v>207</v>
       </c>
       <c r="E172" s="21">
         <f>IF(D172="?OLD","!!!","")</f>
@@ -7999,7 +7967,16 @@
     </row>
     <row r="173" spans="1:12">
       <c r="A173" s="20" t="s">
-        <v>96</v>
+        <v>208</v>
+      </c>
+      <c r="B173" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C173" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D173" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E173" s="21">
         <f>IF(D173="?OLD","!!!","")</f>
@@ -8033,16 +8010,13 @@
     </row>
     <row r="174" spans="1:12">
       <c r="A174" s="20" t="s">
-        <v>97</v>
+        <v>209</v>
       </c>
       <c r="B174" s="27" t="s">
         <v>114</v>
       </c>
       <c r="C174" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D174" s="27" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E174" s="21">
         <f>IF(D174="?OLD","!!!","")</f>
@@ -8110,7 +8084,16 @@
     </row>
     <row r="176" spans="1:12">
       <c r="A176" s="20" t="s">
-        <v>206</v>
+        <v>100</v>
+      </c>
+      <c r="B176" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C176" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D176" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E176" s="21">
         <f>IF(D176="?OLD","!!!","")</f>
@@ -8144,7 +8127,7 @@
     </row>
     <row r="177" spans="1:12">
       <c r="A177" s="20" t="s">
-        <v>207</v>
+        <v>102</v>
       </c>
       <c r="E177" s="21">
         <f>IF(D177="?OLD","!!!","")</f>
@@ -8178,7 +8161,7 @@
     </row>
     <row r="178" spans="1:12">
       <c r="A178" s="20" t="s">
-        <v>125</v>
+        <v>210</v>
       </c>
       <c r="E178" s="21">
         <f>IF(D178="?OLD","!!!","")</f>
@@ -8211,11 +8194,42 @@
       <c r="L178" s="26"/>
     </row>
     <row r="179" spans="1:12">
-      <c r="A179" s="20"/>
+      <c r="A179" s="20" t="s">
+        <v>211</v>
+      </c>
+      <c r="E179" s="21">
+        <f>IF(D179="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F179" s="22" t="str">
+        <f>IF(OR(E179="",E179="!!!"),"",IF(NOT(ISNA(VLOOKUP(E179,E$1:E178,1,FALSE()))),"OLD",IF(AND(E179&lt;&gt;"",E179&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G179" s="23" t="str">
+        <f>IF(OR(E179="",E179="!!!"),"",IF(OR(J179=0,AND(J179=1,K179=1),AND(J179=1,I179="SBJ"),AND(J179=1,I179=0)),"?IN_FOCUS",IF(J179&lt;=2,"?ACTIVATED",IF(J179&lt;&gt;"","?FAMILIAR",IF(F179="NEW",IF(ISNA(VLOOKUP(E179,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H179" s="24" t="str">
+        <f>IF(J179&lt;&gt;1,"",IF(I179="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I179" s="25" t="str">
+        <f>IF(OR(E179="",E179="!!!",F179="NEW"),"",INDEX(B178:B$2,-1+SUMPRODUCT(MAX(ROW(E178:E$2)*(E179=E178:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J179" s="25" t="str">
+        <f>IF(OR(E179="",E179="!!!",F179="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E179)*(E179=E$2:E179)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E178)*(E2=E$1:E178))))))</f>
+        <v> </v>
+      </c>
+      <c r="K179" s="25" t="str">
+        <f>IF(OR(E179="",E179="!!!",F179="NEW"),"",INDEX(J$1:J178,SUMPRODUCT(MAX(ROW(E$1:E178)*(E179=E$1:E178)))))</f>
+        <v> </v>
+      </c>
+      <c r="L179" s="26"/>
     </row>
     <row r="180" spans="1:12">
       <c r="A180" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E180" s="21">
         <f>IF(D180="?OLD","!!!","")</f>
@@ -8248,13 +8262,11 @@
       <c r="L180" s="26"/>
     </row>
     <row r="181" spans="1:12">
-      <c r="A181" s="20" t="s">
-        <v>208</v>
-      </c>
+      <c r="A181" s="20"/>
     </row>
     <row r="182" spans="1:12">
       <c r="A182" s="20" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="E182" s="21">
         <f>IF(D182="?OLD","!!!","")</f>
@@ -8288,50 +8300,12 @@
     </row>
     <row r="183" spans="1:12">
       <c r="A183" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B183" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C183" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D183" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E183" s="21">
-        <f>IF(D183="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F183" s="22" t="str">
-        <f>IF(OR(E183="",E183="!!!"),"",IF(NOT(ISNA(VLOOKUP(E183,E$1:E182,1,FALSE()))),"OLD",IF(AND(E183&lt;&gt;"",E183&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G183" s="23" t="str">
-        <f>IF(OR(E183="",E183="!!!"),"",IF(OR(J183=0,AND(J183=1,K183=1),AND(J183=1,I183="SBJ"),AND(J183=1,I183=0)),"?IN_FOCUS",IF(J183&lt;=2,"?ACTIVATED",IF(J183&lt;&gt;"","?FAMILIAR",IF(F183="NEW",IF(ISNA(VLOOKUP(E183,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H183" s="24" t="str">
-        <f>IF(J183&lt;&gt;1,"",IF(I183="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I183" s="25" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",INDEX(B182:B$2,-1+SUMPRODUCT(MAX(ROW(E182:E$2)*(E183=E182:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J183" s="25" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E183)*(E183=E$2:E183)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E182)*(E2=E$1:E182))))))</f>
-        <v> </v>
-      </c>
-      <c r="K183" s="25" t="str">
-        <f>IF(OR(E183="",E183="!!!",F183="NEW"),"",INDEX(J$1:J182,SUMPRODUCT(MAX(ROW(E$1:E182)*(E183=E$1:E182)))))</f>
-        <v> </v>
-      </c>
-      <c r="L183" s="26"/>
+        <v>212</v>
+      </c>
     </row>
     <row r="184" spans="1:12">
       <c r="A184" s="20" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E184" s="21">
         <f>IF(D184="?OLD","!!!","")</f>
@@ -8365,16 +8339,16 @@
     </row>
     <row r="185" spans="1:12">
       <c r="A185" s="20" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="B185" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C185" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D185" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C185" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D185" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E185" s="21">
         <f>IF(D185="?OLD","!!!","")</f>
@@ -8408,7 +8382,7 @@
     </row>
     <row r="186" spans="1:12">
       <c r="A186" s="20" t="s">
-        <v>203</v>
+        <v>134</v>
       </c>
       <c r="E186" s="21">
         <f>IF(D186="?OLD","!!!","")</f>
@@ -8442,16 +8416,16 @@
     </row>
     <row r="187" spans="1:12">
       <c r="A187" s="20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B187" s="27" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C187" s="27" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D187" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E187" s="21">
         <f>IF(D187="?OLD","!!!","")</f>
@@ -8485,7 +8459,7 @@
     </row>
     <row r="188" spans="1:12">
       <c r="A188" s="20" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="E188" s="21">
         <f>IF(D188="?OLD","!!!","")</f>
@@ -8519,7 +8493,16 @@
     </row>
     <row r="189" spans="1:12">
       <c r="A189" s="20" t="s">
-        <v>105</v>
+        <v>208</v>
+      </c>
+      <c r="B189" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C189" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D189" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E189" s="21">
         <f>IF(D189="?OLD","!!!","")</f>
@@ -8553,7 +8536,7 @@
     </row>
     <row r="190" spans="1:12">
       <c r="A190" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E190" s="21">
         <f>IF(D190="?OLD","!!!","")</f>
@@ -8587,16 +8570,7 @@
     </row>
     <row r="191" spans="1:12">
       <c r="A191" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="B191" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C191" s="27" t="s">
         <v>108</v>
-      </c>
-      <c r="D191" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E191" s="21">
         <f>IF(D191="?OLD","!!!","")</f>
@@ -8630,7 +8604,7 @@
     </row>
     <row r="192" spans="1:12">
       <c r="A192" s="20" t="s">
-        <v>212</v>
+        <v>138</v>
       </c>
       <c r="E192" s="21">
         <f>IF(D192="?OLD","!!!","")</f>
@@ -8664,7 +8638,16 @@
     </row>
     <row r="193" spans="1:12">
       <c r="A193" s="20" t="s">
-        <v>199</v>
+        <v>215</v>
+      </c>
+      <c r="B193" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C193" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D193" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E193" s="21">
         <f>IF(D193="?OLD","!!!","")</f>
@@ -8698,13 +8681,7 @@
     </row>
     <row r="194" spans="1:12">
       <c r="A194" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="B194" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C194" s="27" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E194" s="21">
         <f>IF(D194="?OLD","!!!","")</f>
@@ -8738,7 +8715,7 @@
     </row>
     <row r="195" spans="1:12">
       <c r="A195" s="20" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="E195" s="21">
         <f>IF(D195="?OLD","!!!","")</f>
@@ -8772,7 +8749,13 @@
     </row>
     <row r="196" spans="1:12">
       <c r="A196" s="20" t="s">
-        <v>213</v>
+        <v>183</v>
+      </c>
+      <c r="B196" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C196" s="27" t="s">
+        <v>205</v>
       </c>
       <c r="E196" s="21">
         <f>IF(D196="?OLD","!!!","")</f>
@@ -8806,7 +8789,7 @@
     </row>
     <row r="197" spans="1:12">
       <c r="A197" s="20" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="E197" s="21">
         <f>IF(D197="?OLD","!!!","")</f>
@@ -8840,7 +8823,7 @@
     </row>
     <row r="198" spans="1:12">
       <c r="A198" s="20" t="s">
-        <v>156</v>
+        <v>217</v>
       </c>
       <c r="E198" s="21">
         <f>IF(D198="?OLD","!!!","")</f>
@@ -8874,7 +8857,7 @@
     </row>
     <row r="199" spans="1:12">
       <c r="A199" s="20" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="E199" s="21">
         <f>IF(D199="?OLD","!!!","")</f>
@@ -8908,16 +8891,7 @@
     </row>
     <row r="200" spans="1:12">
       <c r="A200" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="B200" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C200" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D200" s="27" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="E200" s="21">
         <f>IF(D200="?OLD","!!!","")</f>
@@ -8951,7 +8925,7 @@
     </row>
     <row r="201" spans="1:12">
       <c r="A201" s="20" t="s">
-        <v>215</v>
+        <v>121</v>
       </c>
       <c r="E201" s="21">
         <f>IF(D201="?OLD","!!!","")</f>
@@ -8985,7 +8959,16 @@
     </row>
     <row r="202" spans="1:12">
       <c r="A202" s="20" t="s">
-        <v>216</v>
+        <v>218</v>
+      </c>
+      <c r="B202" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C202" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D202" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E202" s="21">
         <f>IF(D202="?OLD","!!!","")</f>
@@ -9019,7 +9002,7 @@
     </row>
     <row r="203" spans="1:12">
       <c r="A203" s="20" t="s">
-        <v>148</v>
+        <v>219</v>
       </c>
       <c r="E203" s="21">
         <f>IF(D203="?OLD","!!!","")</f>
@@ -9053,7 +9036,7 @@
     </row>
     <row r="204" spans="1:12">
       <c r="A204" s="20" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="E204" s="21">
         <f>IF(D204="?OLD","!!!","")</f>
@@ -9086,11 +9069,42 @@
       <c r="L204" s="26"/>
     </row>
     <row r="205" spans="1:12">
-      <c r="A205" s="20"/>
+      <c r="A205" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E205" s="21">
+        <f>IF(D205="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F205" s="22" t="str">
+        <f>IF(OR(E205="",E205="!!!"),"",IF(NOT(ISNA(VLOOKUP(E205,E$1:E204,1,FALSE()))),"OLD",IF(AND(E205&lt;&gt;"",E205&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G205" s="23" t="str">
+        <f>IF(OR(E205="",E205="!!!"),"",IF(OR(J205=0,AND(J205=1,K205=1),AND(J205=1,I205="SBJ"),AND(J205=1,I205=0)),"?IN_FOCUS",IF(J205&lt;=2,"?ACTIVATED",IF(J205&lt;&gt;"","?FAMILIAR",IF(F205="NEW",IF(ISNA(VLOOKUP(E205,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H205" s="24" t="str">
+        <f>IF(J205&lt;&gt;1,"",IF(I205="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I205" s="25" t="str">
+        <f>IF(OR(E205="",E205="!!!",F205="NEW"),"",INDEX(B204:B$2,-1+SUMPRODUCT(MAX(ROW(E204:E$2)*(E205=E204:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J205" s="25" t="str">
+        <f>IF(OR(E205="",E205="!!!",F205="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E205)*(E205=E$2:E205)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E204)*(E2=E$1:E204))))))</f>
+        <v> </v>
+      </c>
+      <c r="K205" s="25" t="str">
+        <f>IF(OR(E205="",E205="!!!",F205="NEW"),"",INDEX(J$1:J204,SUMPRODUCT(MAX(ROW(E$1:E204)*(E205=E$1:E204)))))</f>
+        <v> </v>
+      </c>
+      <c r="L205" s="26"/>
     </row>
     <row r="206" spans="1:12">
       <c r="A206" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E206" s="21">
         <f>IF(D206="?OLD","!!!","")</f>
@@ -9123,13 +9137,11 @@
       <c r="L206" s="26"/>
     </row>
     <row r="207" spans="1:12">
-      <c r="A207" s="20" t="s">
-        <v>217</v>
-      </c>
+      <c r="A207" s="20"/>
     </row>
     <row r="208" spans="1:12">
       <c r="A208" s="20" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E208" s="21">
         <f>IF(D208="?OLD","!!!","")</f>
@@ -9163,50 +9175,12 @@
     </row>
     <row r="209" spans="1:12">
       <c r="A209" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B209" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C209" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D209" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E209" s="21">
-        <f>IF(D209="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F209" s="22" t="str">
-        <f>IF(OR(E209="",E209="!!!"),"",IF(NOT(ISNA(VLOOKUP(E209,E$1:E208,1,FALSE()))),"OLD",IF(AND(E209&lt;&gt;"",E209&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G209" s="23" t="str">
-        <f>IF(OR(E209="",E209="!!!"),"",IF(OR(J209=0,AND(J209=1,K209=1),AND(J209=1,I209="SBJ"),AND(J209=1,I209=0)),"?IN_FOCUS",IF(J209&lt;=2,"?ACTIVATED",IF(J209&lt;&gt;"","?FAMILIAR",IF(F209="NEW",IF(ISNA(VLOOKUP(E209,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H209" s="24" t="str">
-        <f>IF(J209&lt;&gt;1,"",IF(I209="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I209" s="25" t="str">
-        <f>IF(OR(E209="",E209="!!!",F209="NEW"),"",INDEX(B208:B$2,-1+SUMPRODUCT(MAX(ROW(E208:E$2)*(E209=E208:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J209" s="25" t="str">
-        <f>IF(OR(E209="",E209="!!!",F209="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E209)*(E209=E$2:E209)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E208)*(E2=E$1:E208))))))</f>
-        <v> </v>
-      </c>
-      <c r="K209" s="25" t="str">
-        <f>IF(OR(E209="",E209="!!!",F209="NEW"),"",INDEX(J$1:J208,SUMPRODUCT(MAX(ROW(E$1:E208)*(E209=E$1:E208)))))</f>
-        <v> </v>
-      </c>
-      <c r="L209" s="26"/>
+        <v>221</v>
+      </c>
     </row>
     <row r="210" spans="1:12">
       <c r="A210" s="20" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
       <c r="E210" s="21">
         <f>IF(D210="?OLD","!!!","")</f>
@@ -9240,7 +9214,16 @@
     </row>
     <row r="211" spans="1:12">
       <c r="A211" s="20" t="s">
-        <v>219</v>
+        <v>222</v>
+      </c>
+      <c r="B211" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C211" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D211" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E211" s="21">
         <f>IF(D211="?OLD","!!!","")</f>
@@ -9274,7 +9257,7 @@
     </row>
     <row r="212" spans="1:12">
       <c r="A212" s="20" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="E212" s="21">
         <f>IF(D212="?OLD","!!!","")</f>
@@ -9308,13 +9291,7 @@
     </row>
     <row r="213" spans="1:12">
       <c r="A213" s="20" t="s">
-        <v>221</v>
-      </c>
-      <c r="B213" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C213" s="27" t="s">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="E213" s="21">
         <f>IF(D213="?OLD","!!!","")</f>
@@ -9348,7 +9325,7 @@
     </row>
     <row r="214" spans="1:12">
       <c r="A214" s="20" t="s">
-        <v>105</v>
+        <v>224</v>
       </c>
       <c r="E214" s="21">
         <f>IF(D214="?OLD","!!!","")</f>
@@ -9382,16 +9359,13 @@
     </row>
     <row r="215" spans="1:12">
       <c r="A215" s="20" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B215" s="27" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C215" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D215" s="27" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="E215" s="21">
         <f>IF(D215="?OLD","!!!","")</f>
@@ -9425,7 +9399,7 @@
     </row>
     <row r="216" spans="1:12">
       <c r="A216" s="20" t="s">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="E216" s="21">
         <f>IF(D216="?OLD","!!!","")</f>
@@ -9459,7 +9433,16 @@
     </row>
     <row r="217" spans="1:12">
       <c r="A217" s="20" t="s">
-        <v>224</v>
+        <v>226</v>
+      </c>
+      <c r="B217" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C217" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D217" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E217" s="21">
         <f>IF(D217="?OLD","!!!","")</f>
@@ -9493,7 +9476,7 @@
     </row>
     <row r="218" spans="1:12">
       <c r="A218" s="20" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E218" s="21">
         <f>IF(D218="?OLD","!!!","")</f>
@@ -9527,13 +9510,7 @@
     </row>
     <row r="219" spans="1:12">
       <c r="A219" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B219" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C219" s="27" t="s">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="E219" s="21">
         <f>IF(D219="?OLD","!!!","")</f>
@@ -9567,7 +9544,7 @@
     </row>
     <row r="220" spans="1:12">
       <c r="A220" s="20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E220" s="21">
         <f>IF(D220="?OLD","!!!","")</f>
@@ -9601,7 +9578,13 @@
     </row>
     <row r="221" spans="1:12">
       <c r="A221" s="20" t="s">
-        <v>183</v>
+        <v>230</v>
+      </c>
+      <c r="B221" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C221" s="27" t="s">
+        <v>128</v>
       </c>
       <c r="E221" s="21">
         <f>IF(D221="?OLD","!!!","")</f>
@@ -9635,16 +9618,7 @@
     </row>
     <row r="222" spans="1:12">
       <c r="A222" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="B222" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C222" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D222" s="27" t="s">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="E222" s="21">
         <f>IF(D222="?OLD","!!!","")</f>
@@ -9678,7 +9652,7 @@
     </row>
     <row r="223" spans="1:12">
       <c r="A223" s="20" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="E223" s="21">
         <f>IF(D223="?OLD","!!!","")</f>
@@ -9712,16 +9686,16 @@
     </row>
     <row r="224" spans="1:12">
       <c r="A224" s="20" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B224" s="27" t="s">
-        <v>231</v>
+        <v>110</v>
       </c>
       <c r="C224" s="27" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="D224" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E224" s="21">
         <f>IF(D224="?OLD","!!!","")</f>
@@ -9755,7 +9729,7 @@
     </row>
     <row r="225" spans="1:12">
       <c r="A225" s="20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E225" s="21">
         <f>IF(D225="?OLD","!!!","")</f>
@@ -9789,7 +9763,16 @@
     </row>
     <row r="226" spans="1:12">
       <c r="A226" s="20" t="s">
-        <v>233</v>
+        <v>234</v>
+      </c>
+      <c r="B226" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C226" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D226" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E226" s="21">
         <f>IF(D226="?OLD","!!!","")</f>
@@ -9823,7 +9806,7 @@
     </row>
     <row r="227" spans="1:12">
       <c r="A227" s="20" t="s">
-        <v>105</v>
+        <v>236</v>
       </c>
       <c r="E227" s="21">
         <f>IF(D227="?OLD","!!!","")</f>
@@ -9857,7 +9840,7 @@
     </row>
     <row r="228" spans="1:12">
       <c r="A228" s="20" t="s">
-        <v>148</v>
+        <v>237</v>
       </c>
       <c r="E228" s="21">
         <f>IF(D228="?OLD","!!!","")</f>
@@ -9891,7 +9874,7 @@
     </row>
     <row r="229" spans="1:12">
       <c r="A229" s="20" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E229" s="21">
         <f>IF(D229="?OLD","!!!","")</f>
@@ -9925,7 +9908,7 @@
     </row>
     <row r="230" spans="1:12">
       <c r="A230" s="20" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="E230" s="21">
         <f>IF(D230="?OLD","!!!","")</f>
@@ -9959,16 +9942,7 @@
     </row>
     <row r="231" spans="1:12">
       <c r="A231" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="B231" s="27" t="s">
         <v>136</v>
-      </c>
-      <c r="C231" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D231" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E231" s="21">
         <f>IF(D231="?OLD","!!!","")</f>
@@ -10002,7 +9976,7 @@
     </row>
     <row r="232" spans="1:12">
       <c r="A232" s="20" t="s">
-        <v>234</v>
+        <v>109</v>
       </c>
       <c r="E232" s="21">
         <f>IF(D232="?OLD","!!!","")</f>
@@ -10036,7 +10010,16 @@
     </row>
     <row r="233" spans="1:12">
       <c r="A233" s="20" t="s">
-        <v>125</v>
+        <v>213</v>
+      </c>
+      <c r="B233" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C233" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D233" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E233" s="21">
         <f>IF(D233="?OLD","!!!","")</f>
@@ -10069,99 +10052,93 @@
       <c r="L233" s="26"/>
     </row>
     <row r="234" spans="1:12">
-      <c r="A234" s="20"/>
+      <c r="A234" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="E234" s="21">
+        <f>IF(D234="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F234" s="22" t="str">
+        <f>IF(OR(E234="",E234="!!!"),"",IF(NOT(ISNA(VLOOKUP(E234,E$1:E233,1,FALSE()))),"OLD",IF(AND(E234&lt;&gt;"",E234&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G234" s="23" t="str">
+        <f>IF(OR(E234="",E234="!!!"),"",IF(OR(J234=0,AND(J234=1,K234=1),AND(J234=1,I234="SBJ"),AND(J234=1,I234=0)),"?IN_FOCUS",IF(J234&lt;=2,"?ACTIVATED",IF(J234&lt;&gt;"","?FAMILIAR",IF(F234="NEW",IF(ISNA(VLOOKUP(E234,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H234" s="24" t="str">
+        <f>IF(J234&lt;&gt;1,"",IF(I234="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I234" s="25" t="str">
+        <f>IF(OR(E234="",E234="!!!",F234="NEW"),"",INDEX(B233:B$2,-1+SUMPRODUCT(MAX(ROW(E233:E$2)*(E234=E233:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J234" s="25" t="str">
+        <f>IF(OR(E234="",E234="!!!",F234="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E234)*(E234=E$2:E234)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E233)*(E2=E$1:E233))))))</f>
+        <v> </v>
+      </c>
+      <c r="K234" s="25" t="str">
+        <f>IF(OR(E234="",E234="!!!",F234="NEW"),"",INDEX(J$1:J233,SUMPRODUCT(MAX(ROW(E$1:E233)*(E234=E$1:E233)))))</f>
+        <v> </v>
+      </c>
+      <c r="L234" s="26"/>
     </row>
     <row r="235" spans="1:12">
       <c r="A235" s="20" t="s">
-        <v>235</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E235" s="21">
+        <f>IF(D235="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F235" s="22" t="str">
+        <f>IF(OR(E235="",E235="!!!"),"",IF(NOT(ISNA(VLOOKUP(E235,E$1:E234,1,FALSE()))),"OLD",IF(AND(E235&lt;&gt;"",E235&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G235" s="23" t="str">
+        <f>IF(OR(E235="",E235="!!!"),"",IF(OR(J235=0,AND(J235=1,K235=1),AND(J235=1,I235="SBJ"),AND(J235=1,I235=0)),"?IN_FOCUS",IF(J235&lt;=2,"?ACTIVATED",IF(J235&lt;&gt;"","?FAMILIAR",IF(F235="NEW",IF(ISNA(VLOOKUP(E235,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H235" s="24" t="str">
+        <f>IF(J235&lt;&gt;1,"",IF(I235="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I235" s="25" t="str">
+        <f>IF(OR(E235="",E235="!!!",F235="NEW"),"",INDEX(B234:B$2,-1+SUMPRODUCT(MAX(ROW(E234:E$2)*(E235=E234:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J235" s="25" t="str">
+        <f>IF(OR(E235="",E235="!!!",F235="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E235)*(E235=E$2:E235)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E234)*(E2=E$1:E234))))))</f>
+        <v> </v>
+      </c>
+      <c r="K235" s="25" t="str">
+        <f>IF(OR(E235="",E235="!!!",F235="NEW"),"",INDEX(J$1:J234,SUMPRODUCT(MAX(ROW(E$1:E234)*(E235=E$1:E234)))))</f>
+        <v> </v>
+      </c>
+      <c r="L235" s="26"/>
     </row>
     <row r="236" spans="1:12">
-      <c r="A236" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B236" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C236" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="D236" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E236" s="21">
-        <f>IF(D236="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F236" s="22" t="str">
-        <f>IF(OR(E236="",E236="!!!"),"",IF(NOT(ISNA(VLOOKUP(E236,E$1:E235,1,FALSE()))),"OLD",IF(AND(E236&lt;&gt;"",E236&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G236" s="23" t="str">
-        <f>IF(OR(E236="",E236="!!!"),"",IF(OR(J236=0,AND(J236=1,K236=1),AND(J236=1,I236="SBJ"),AND(J236=1,I236=0)),"?IN_FOCUS",IF(J236&lt;=2,"?ACTIVATED",IF(J236&lt;&gt;"","?FAMILIAR",IF(F236="NEW",IF(ISNA(VLOOKUP(E236,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H236" s="24" t="str">
-        <f>IF(J236&lt;&gt;1,"",IF(I236="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I236" s="25" t="str">
-        <f>IF(OR(E236="",E236="!!!",F236="NEW"),"",INDEX(B235:B$2,-1+SUMPRODUCT(MAX(ROW(E235:E$2)*(E236=E235:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J236" s="25" t="str">
-        <f>IF(OR(E236="",E236="!!!",F236="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E236)*(E236=E$2:E236)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E235)*(E2=E$1:E235))))))</f>
-        <v> </v>
-      </c>
-      <c r="K236" s="25" t="str">
-        <f>IF(OR(E236="",E236="!!!",F236="NEW"),"",INDEX(J$1:J235,SUMPRODUCT(MAX(ROW(E$1:E235)*(E236=E$1:E235)))))</f>
-        <v> </v>
-      </c>
-      <c r="L236" s="26"/>
+      <c r="A236" s="20"/>
     </row>
     <row r="237" spans="1:12">
       <c r="A237" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="B237" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C237" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="E237" s="21">
-        <f>IF(D237="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F237" s="22" t="str">
-        <f>IF(OR(E237="",E237="!!!"),"",IF(NOT(ISNA(VLOOKUP(E237,E$1:E236,1,FALSE()))),"OLD",IF(AND(E237&lt;&gt;"",E237&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G237" s="23" t="str">
-        <f>IF(OR(E237="",E237="!!!"),"",IF(OR(J237=0,AND(J237=1,K237=1),AND(J237=1,I237="SBJ"),AND(J237=1,I237=0)),"?IN_FOCUS",IF(J237&lt;=2,"?ACTIVATED",IF(J237&lt;&gt;"","?FAMILIAR",IF(F237="NEW",IF(ISNA(VLOOKUP(E237,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H237" s="24" t="str">
-        <f>IF(J237&lt;&gt;1,"",IF(I237="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I237" s="25" t="str">
-        <f>IF(OR(E237="",E237="!!!",F237="NEW"),"",INDEX(B236:B$2,-1+SUMPRODUCT(MAX(ROW(E236:E$2)*(E237=E236:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J237" s="25" t="str">
-        <f>IF(OR(E237="",E237="!!!",F237="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E237)*(E237=E$2:E237)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E236)*(E2=E$1:E236))))))</f>
-        <v> </v>
-      </c>
-      <c r="K237" s="25" t="str">
-        <f>IF(OR(E237="",E237="!!!",F237="NEW"),"",INDEX(J$1:J236,SUMPRODUCT(MAX(ROW(E$1:E236)*(E237=E$1:E236)))))</f>
-        <v> </v>
-      </c>
-      <c r="L237" s="26"/>
+        <v>239</v>
+      </c>
     </row>
     <row r="238" spans="1:12">
       <c r="A238" s="20" t="s">
-        <v>183</v>
+        <v>240</v>
+      </c>
+      <c r="B238" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C238" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="D238" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E238" s="21">
         <f>IF(D238="?OLD","!!!","")</f>
@@ -10195,16 +10172,13 @@
     </row>
     <row r="239" spans="1:12">
       <c r="A239" s="20" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B239" s="27" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="D239" s="27" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E239" s="21">
         <f>IF(D239="?OLD","!!!","")</f>
@@ -10238,13 +10212,7 @@
     </row>
     <row r="240" spans="1:12">
       <c r="A240" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="B240" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C240" s="27" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="E240" s="21">
         <f>IF(D240="?OLD","!!!","")</f>
@@ -10278,7 +10246,16 @@
     </row>
     <row r="241" spans="1:12">
       <c r="A241" s="20" t="s">
-        <v>186</v>
+        <v>243</v>
+      </c>
+      <c r="B241" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C241" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="D241" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E241" s="21">
         <f>IF(D241="?OLD","!!!","")</f>
@@ -10312,7 +10289,13 @@
     </row>
     <row r="242" spans="1:12">
       <c r="A242" s="20" t="s">
-        <v>96</v>
+        <v>244</v>
+      </c>
+      <c r="B242" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C242" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="E242" s="21">
         <f>IF(D242="?OLD","!!!","")</f>
@@ -10346,16 +10329,7 @@
     </row>
     <row r="243" spans="1:12">
       <c r="A243" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B243" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C243" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="D243" s="27" t="s">
-        <v>95</v>
+        <v>189</v>
       </c>
       <c r="E243" s="21">
         <f>IF(D243="?OLD","!!!","")</f>
@@ -10389,7 +10363,7 @@
     </row>
     <row r="244" spans="1:12">
       <c r="A244" s="20" t="s">
-        <v>243</v>
+        <v>99</v>
       </c>
       <c r="E244" s="21">
         <f>IF(D244="?OLD","!!!","")</f>
@@ -10423,16 +10397,16 @@
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B245" s="27" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="C245" s="27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D245" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E245" s="21">
         <f>IF(D245="?OLD","!!!","")</f>
@@ -10466,7 +10440,7 @@
     </row>
     <row r="246" spans="1:12">
       <c r="A246" s="20" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="E246" s="21">
         <f>IF(D246="?OLD","!!!","")</f>
@@ -10500,16 +10474,16 @@
     </row>
     <row r="247" spans="1:12">
       <c r="A247" s="20" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B247" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C247" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="D247" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C247" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D247" s="27" t="s">
-        <v>95</v>
       </c>
       <c r="E247" s="21">
         <f>IF(D247="?OLD","!!!","")</f>
@@ -10543,16 +10517,7 @@
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B248" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C248" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D248" s="27" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="E248" s="21">
         <f>IF(D248="?OLD","!!!","")</f>
@@ -10586,7 +10551,16 @@
     </row>
     <row r="249" spans="1:12">
       <c r="A249" s="20" t="s">
-        <v>183</v>
+        <v>250</v>
+      </c>
+      <c r="B249" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C249" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D249" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E249" s="21">
         <f>IF(D249="?OLD","!!!","")</f>
@@ -10620,13 +10594,16 @@
     </row>
     <row r="250" spans="1:12">
       <c r="A250" s="20" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B250" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C250" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D250" s="27" t="s">
         <v>98</v>
-      </c>
-      <c r="C250" s="27" t="s">
-        <v>112</v>
       </c>
       <c r="E250" s="21">
         <f>IF(D250="?OLD","!!!","")</f>
@@ -10660,7 +10637,7 @@
     </row>
     <row r="251" spans="1:12">
       <c r="A251" s="20" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="E251" s="21">
         <f>IF(D251="?OLD","!!!","")</f>
@@ -10693,11 +10670,48 @@
       <c r="L251" s="26"/>
     </row>
     <row r="252" spans="1:12">
-      <c r="A252" s="20"/>
+      <c r="A252" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="B252" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C252" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E252" s="21">
+        <f>IF(D252="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F252" s="22" t="str">
+        <f>IF(OR(E252="",E252="!!!"),"",IF(NOT(ISNA(VLOOKUP(E252,E$1:E251,1,FALSE()))),"OLD",IF(AND(E252&lt;&gt;"",E252&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G252" s="23" t="str">
+        <f>IF(OR(E252="",E252="!!!"),"",IF(OR(J252=0,AND(J252=1,K252=1),AND(J252=1,I252="SBJ"),AND(J252=1,I252=0)),"?IN_FOCUS",IF(J252&lt;=2,"?ACTIVATED",IF(J252&lt;&gt;"","?FAMILIAR",IF(F252="NEW",IF(ISNA(VLOOKUP(E252,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H252" s="24" t="str">
+        <f>IF(J252&lt;&gt;1,"",IF(I252="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I252" s="25" t="str">
+        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",INDEX(B251:B$2,-1+SUMPRODUCT(MAX(ROW(E251:E$2)*(E252=E251:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J252" s="25" t="str">
+        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E252)*(E252=E$2:E252)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E251)*(E2=E$1:E251))))))</f>
+        <v> </v>
+      </c>
+      <c r="K252" s="25" t="str">
+        <f>IF(OR(E252="",E252="!!!",F252="NEW"),"",INDEX(J$1:J251,SUMPRODUCT(MAX(ROW(E$1:E251)*(E252=E$1:E251)))))</f>
+        <v> </v>
+      </c>
+      <c r="L252" s="26"/>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E253" s="21">
         <f>IF(D253="?OLD","!!!","")</f>
@@ -10730,22 +10744,11 @@
       <c r="L253" s="26"/>
     </row>
     <row r="254" spans="1:12">
-      <c r="A254" s="20" t="s">
-        <v>248</v>
-      </c>
+      <c r="A254" s="20"/>
     </row>
     <row r="255" spans="1:12">
       <c r="A255" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B255" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C255" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D255" s="27" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="E255" s="21">
         <f>IF(D255="?OLD","!!!","")</f>
@@ -10779,41 +10782,21 @@
     </row>
     <row r="256" spans="1:12">
       <c r="A256" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="E256" s="21">
-        <f>IF(D256="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F256" s="22" t="str">
-        <f>IF(OR(E256="",E256="!!!"),"",IF(NOT(ISNA(VLOOKUP(E256,E$1:E255,1,FALSE()))),"OLD",IF(AND(E256&lt;&gt;"",E256&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G256" s="23" t="str">
-        <f>IF(OR(E256="",E256="!!!"),"",IF(OR(J256=0,AND(J256=1,K256=1),AND(J256=1,I256="SBJ"),AND(J256=1,I256=0)),"?IN_FOCUS",IF(J256&lt;=2,"?ACTIVATED",IF(J256&lt;&gt;"","?FAMILIAR",IF(F256="NEW",IF(ISNA(VLOOKUP(E256,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H256" s="24" t="str">
-        <f>IF(J256&lt;&gt;1,"",IF(I256="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I256" s="25" t="str">
-        <f>IF(OR(E256="",E256="!!!",F256="NEW"),"",INDEX(B255:B$2,-1+SUMPRODUCT(MAX(ROW(E255:E$2)*(E256=E255:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J256" s="25" t="str">
-        <f>IF(OR(E256="",E256="!!!",F256="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E256)*(E256=E$2:E256)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E255)*(E2=E$1:E255))))))</f>
-        <v> </v>
-      </c>
-      <c r="K256" s="25" t="str">
-        <f>IF(OR(E256="",E256="!!!",F256="NEW"),"",INDEX(J$1:J255,SUMPRODUCT(MAX(ROW(E$1:E255)*(E256=E$1:E255)))))</f>
-        <v> </v>
-      </c>
-      <c r="L256" s="26"/>
+        <v>252</v>
+      </c>
     </row>
     <row r="257" spans="1:12">
       <c r="A257" s="20" t="s">
-        <v>249</v>
+        <v>191</v>
+      </c>
+      <c r="B257" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C257" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D257" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E257" s="21">
         <f>IF(D257="?OLD","!!!","")</f>
@@ -10847,7 +10830,7 @@
     </row>
     <row r="258" spans="1:12">
       <c r="A258" s="20" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="E258" s="21">
         <f>IF(D258="?OLD","!!!","")</f>
@@ -10881,7 +10864,7 @@
     </row>
     <row r="259" spans="1:12">
       <c r="A259" s="20" t="s">
-        <v>105</v>
+        <v>253</v>
       </c>
       <c r="E259" s="21">
         <f>IF(D259="?OLD","!!!","")</f>
@@ -10915,7 +10898,7 @@
     </row>
     <row r="260" spans="1:12">
       <c r="A260" s="20" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="E260" s="21">
         <f>IF(D260="?OLD","!!!","")</f>
@@ -10949,16 +10932,7 @@
     </row>
     <row r="261" spans="1:12">
       <c r="A261" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="B261" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C261" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D261" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E261" s="21">
         <f>IF(D261="?OLD","!!!","")</f>
@@ -10992,7 +10966,7 @@
     </row>
     <row r="262" spans="1:12">
       <c r="A262" s="20" t="s">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="E262" s="21">
         <f>IF(D262="?OLD","!!!","")</f>
@@ -11026,7 +11000,16 @@
     </row>
     <row r="263" spans="1:12">
       <c r="A263" s="20" t="s">
-        <v>96</v>
+        <v>171</v>
+      </c>
+      <c r="B263" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C263" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D263" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E263" s="21">
         <f>IF(D263="?OLD","!!!","")</f>
@@ -11060,13 +11043,7 @@
     </row>
     <row r="264" spans="1:12">
       <c r="A264" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="B264" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C264" s="27" t="s">
-        <v>112</v>
+        <v>254</v>
       </c>
       <c r="E264" s="21">
         <f>IF(D264="?OLD","!!!","")</f>
@@ -11100,7 +11077,7 @@
     </row>
     <row r="265" spans="1:12">
       <c r="A265" s="20" t="s">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c r="E265" s="21">
         <f>IF(D265="?OLD","!!!","")</f>
@@ -11134,7 +11111,13 @@
     </row>
     <row r="266" spans="1:12">
       <c r="A266" s="20" t="s">
-        <v>105</v>
+        <v>255</v>
+      </c>
+      <c r="B266" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C266" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="E266" s="21">
         <f>IF(D266="?OLD","!!!","")</f>
@@ -11168,7 +11151,7 @@
     </row>
     <row r="267" spans="1:12">
       <c r="A267" s="20" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E267" s="21">
         <f>IF(D267="?OLD","!!!","")</f>
@@ -11202,7 +11185,7 @@
     </row>
     <row r="268" spans="1:12">
       <c r="A268" s="20" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="E268" s="21">
         <f>IF(D268="?OLD","!!!","")</f>
@@ -11236,7 +11219,7 @@
     </row>
     <row r="269" spans="1:12">
       <c r="A269" s="20" t="s">
-        <v>105</v>
+        <v>257</v>
       </c>
       <c r="E269" s="21">
         <f>IF(D269="?OLD","!!!","")</f>
@@ -11270,7 +11253,7 @@
     </row>
     <row r="270" spans="1:12">
       <c r="A270" s="20" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E270" s="21">
         <f>IF(D270="?OLD","!!!","")</f>
@@ -11304,7 +11287,7 @@
     </row>
     <row r="271" spans="1:12">
       <c r="A271" s="20" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="E271" s="21">
         <f>IF(D271="?OLD","!!!","")</f>
@@ -11338,16 +11321,7 @@
     </row>
     <row r="272" spans="1:12">
       <c r="A272" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="B272" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C272" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D272" s="27" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E272" s="21">
         <f>IF(D272="?OLD","!!!","")</f>
@@ -11381,7 +11355,7 @@
     </row>
     <row r="273" spans="1:12">
       <c r="A273" s="20" t="s">
-        <v>255</v>
+        <v>175</v>
       </c>
       <c r="E273" s="21">
         <f>IF(D273="?OLD","!!!","")</f>
@@ -11415,16 +11389,16 @@
     </row>
     <row r="274" spans="1:12">
       <c r="A274" s="20" t="s">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="B274" s="27" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C274" s="27" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D274" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E274" s="21">
         <f>IF(D274="?OLD","!!!","")</f>
@@ -11458,7 +11432,7 @@
     </row>
     <row r="275" spans="1:12">
       <c r="A275" s="20" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E275" s="21">
         <f>IF(D275="?OLD","!!!","")</f>
@@ -11492,7 +11466,16 @@
     </row>
     <row r="276" spans="1:12">
       <c r="A276" s="20" t="s">
-        <v>154</v>
+        <v>234</v>
+      </c>
+      <c r="B276" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C276" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D276" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E276" s="21">
         <f>IF(D276="?OLD","!!!","")</f>
@@ -11526,7 +11509,7 @@
     </row>
     <row r="277" spans="1:12">
       <c r="A277" s="20" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E277" s="21">
         <f>IF(D277="?OLD","!!!","")</f>
@@ -11560,7 +11543,7 @@
     </row>
     <row r="278" spans="1:12">
       <c r="A278" s="20" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="E278" s="21">
         <f>IF(D278="?OLD","!!!","")</f>
@@ -11594,7 +11577,7 @@
     </row>
     <row r="279" spans="1:12">
       <c r="A279" s="20" t="s">
-        <v>148</v>
+        <v>261</v>
       </c>
       <c r="E279" s="21">
         <f>IF(D279="?OLD","!!!","")</f>
@@ -11627,11 +11610,42 @@
       <c r="L279" s="26"/>
     </row>
     <row r="280" spans="1:12">
-      <c r="A280" s="20"/>
+      <c r="A280" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E280" s="21">
+        <f>IF(D280="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F280" s="22" t="str">
+        <f>IF(OR(E280="",E280="!!!"),"",IF(NOT(ISNA(VLOOKUP(E280,E$1:E279,1,FALSE()))),"OLD",IF(AND(E280&lt;&gt;"",E280&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G280" s="23" t="str">
+        <f>IF(OR(E280="",E280="!!!"),"",IF(OR(J280=0,AND(J280=1,K280=1),AND(J280=1,I280="SBJ"),AND(J280=1,I280=0)),"?IN_FOCUS",IF(J280&lt;=2,"?ACTIVATED",IF(J280&lt;&gt;"","?FAMILIAR",IF(F280="NEW",IF(ISNA(VLOOKUP(E280,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H280" s="24" t="str">
+        <f>IF(J280&lt;&gt;1,"",IF(I280="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I280" s="25" t="str">
+        <f>IF(OR(E280="",E280="!!!",F280="NEW"),"",INDEX(B279:B$2,-1+SUMPRODUCT(MAX(ROW(E279:E$2)*(E280=E279:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J280" s="25" t="str">
+        <f>IF(OR(E280="",E280="!!!",F280="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E280)*(E280=E$2:E280)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E279)*(E2=E$1:E279))))))</f>
+        <v> </v>
+      </c>
+      <c r="K280" s="25" t="str">
+        <f>IF(OR(E280="",E280="!!!",F280="NEW"),"",INDEX(J$1:J279,SUMPRODUCT(MAX(ROW(E$1:E279)*(E280=E$1:E279)))))</f>
+        <v> </v>
+      </c>
+      <c r="L280" s="26"/>
     </row>
     <row r="281" spans="1:12">
       <c r="A281" s="20" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="E281" s="21">
         <f>IF(D281="?OLD","!!!","")</f>
@@ -11664,13 +11678,11 @@
       <c r="L281" s="26"/>
     </row>
     <row r="282" spans="1:12">
-      <c r="A282" s="20" t="s">
-        <v>258</v>
-      </c>
+      <c r="A282" s="20"/>
     </row>
     <row r="283" spans="1:12">
       <c r="A283" s="20" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E283" s="21">
         <f>IF(D283="?OLD","!!!","")</f>
@@ -11704,50 +11716,12 @@
     </row>
     <row r="284" spans="1:12">
       <c r="A284" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B284" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C284" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D284" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E284" s="21">
-        <f>IF(D284="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F284" s="22" t="str">
-        <f>IF(OR(E284="",E284="!!!"),"",IF(NOT(ISNA(VLOOKUP(E284,E$1:E283,1,FALSE()))),"OLD",IF(AND(E284&lt;&gt;"",E284&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G284" s="23" t="str">
-        <f>IF(OR(E284="",E284="!!!"),"",IF(OR(J284=0,AND(J284=1,K284=1),AND(J284=1,I284="SBJ"),AND(J284=1,I284=0)),"?IN_FOCUS",IF(J284&lt;=2,"?ACTIVATED",IF(J284&lt;&gt;"","?FAMILIAR",IF(F284="NEW",IF(ISNA(VLOOKUP(E284,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H284" s="24" t="str">
-        <f>IF(J284&lt;&gt;1,"",IF(I284="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I284" s="25" t="str">
-        <f>IF(OR(E284="",E284="!!!",F284="NEW"),"",INDEX(B283:B$2,-1+SUMPRODUCT(MAX(ROW(E283:E$2)*(E284=E283:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J284" s="25" t="str">
-        <f>IF(OR(E284="",E284="!!!",F284="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E284)*(E284=E$2:E284)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E283)*(E2=E$1:E283))))))</f>
-        <v> </v>
-      </c>
-      <c r="K284" s="25" t="str">
-        <f>IF(OR(E284="",E284="!!!",F284="NEW"),"",INDEX(J$1:J283,SUMPRODUCT(MAX(ROW(E$1:E283)*(E284=E$1:E283)))))</f>
-        <v> </v>
-      </c>
-      <c r="L284" s="26"/>
+        <v>262</v>
+      </c>
     </row>
     <row r="285" spans="1:12">
       <c r="A285" s="20" t="s">
-        <v>260</v>
+        <v>152</v>
       </c>
       <c r="E285" s="21">
         <f>IF(D285="?OLD","!!!","")</f>
@@ -11781,7 +11755,16 @@
     </row>
     <row r="286" spans="1:12">
       <c r="A286" s="20" t="s">
-        <v>224</v>
+        <v>263</v>
+      </c>
+      <c r="B286" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C286" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D286" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E286" s="21">
         <f>IF(D286="?OLD","!!!","")</f>
@@ -11815,13 +11798,7 @@
     </row>
     <row r="287" spans="1:12">
       <c r="A287" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="B287" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C287" s="27" t="s">
-        <v>124</v>
+        <v>264</v>
       </c>
       <c r="E287" s="21">
         <f>IF(D287="?OLD","!!!","")</f>
@@ -11855,7 +11832,7 @@
     </row>
     <row r="288" spans="1:12">
       <c r="A288" s="20" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="E288" s="21">
         <f>IF(D288="?OLD","!!!","")</f>
@@ -11889,16 +11866,13 @@
     </row>
     <row r="289" spans="1:12">
       <c r="A289" s="20" t="s">
-        <v>135</v>
+        <v>265</v>
       </c>
       <c r="B289" s="27" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="C289" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D289" s="27" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="E289" s="21">
         <f>IF(D289="?OLD","!!!","")</f>
@@ -11932,7 +11906,7 @@
     </row>
     <row r="290" spans="1:12">
       <c r="A290" s="20" t="s">
-        <v>207</v>
+        <v>108</v>
       </c>
       <c r="E290" s="21">
         <f>IF(D290="?OLD","!!!","")</f>
@@ -11966,7 +11940,16 @@
     </row>
     <row r="291" spans="1:12">
       <c r="A291" s="20" t="s">
-        <v>224</v>
+        <v>139</v>
+      </c>
+      <c r="B291" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C291" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D291" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E291" s="21">
         <f>IF(D291="?OLD","!!!","")</f>
@@ -12000,13 +11983,7 @@
     </row>
     <row r="292" spans="1:12">
       <c r="A292" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="B292" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C292" s="27" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="E292" s="21">
         <f>IF(D292="?OLD","!!!","")</f>
@@ -12040,7 +12017,7 @@
     </row>
     <row r="293" spans="1:12">
       <c r="A293" s="20" t="s">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="E293" s="21">
         <f>IF(D293="?OLD","!!!","")</f>
@@ -12074,7 +12051,13 @@
     </row>
     <row r="294" spans="1:12">
       <c r="A294" s="20" t="s">
-        <v>148</v>
+        <v>266</v>
+      </c>
+      <c r="B294" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C294" s="27" t="s">
+        <v>128</v>
       </c>
       <c r="E294" s="21">
         <f>IF(D294="?OLD","!!!","")</f>
@@ -12108,7 +12091,7 @@
     </row>
     <row r="295" spans="1:12">
       <c r="A295" s="20" t="s">
-        <v>171</v>
+        <v>108</v>
       </c>
       <c r="E295" s="21">
         <f>IF(D295="?OLD","!!!","")</f>
@@ -12142,16 +12125,7 @@
     </row>
     <row r="296" spans="1:12">
       <c r="A296" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B296" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="C296" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D296" s="27" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E296" s="21">
         <f>IF(D296="?OLD","!!!","")</f>
@@ -12185,7 +12159,7 @@
     </row>
     <row r="297" spans="1:12">
       <c r="A297" s="20" t="s">
-        <v>263</v>
+        <v>174</v>
       </c>
       <c r="E297" s="21">
         <f>IF(D297="?OLD","!!!","")</f>
@@ -12221,6 +12195,15 @@
       <c r="A298" s="20" t="s">
         <v>191</v>
       </c>
+      <c r="B298" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C298" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D298" s="27" t="s">
+        <v>98</v>
+      </c>
       <c r="E298" s="21">
         <f>IF(D298="?OLD","!!!","")</f>
         <v/>
@@ -12253,7 +12236,7 @@
     </row>
     <row r="299" spans="1:12">
       <c r="A299" s="20" t="s">
-        <v>175</v>
+        <v>267</v>
       </c>
       <c r="E299" s="21">
         <f>IF(D299="?OLD","!!!","")</f>
@@ -12287,7 +12270,7 @@
     </row>
     <row r="300" spans="1:12">
       <c r="A300" s="20" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="E300" s="21">
         <f>IF(D300="?OLD","!!!","")</f>
@@ -12320,93 +12303,93 @@
       <c r="L300" s="26"/>
     </row>
     <row r="301" spans="1:12">
-      <c r="A301" s="20"/>
+      <c r="A301" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="E301" s="21">
+        <f>IF(D301="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F301" s="22" t="str">
+        <f>IF(OR(E301="",E301="!!!"),"",IF(NOT(ISNA(VLOOKUP(E301,E$1:E300,1,FALSE()))),"OLD",IF(AND(E301&lt;&gt;"",E301&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G301" s="23" t="str">
+        <f>IF(OR(E301="",E301="!!!"),"",IF(OR(J301=0,AND(J301=1,K301=1),AND(J301=1,I301="SBJ"),AND(J301=1,I301=0)),"?IN_FOCUS",IF(J301&lt;=2,"?ACTIVATED",IF(J301&lt;&gt;"","?FAMILIAR",IF(F301="NEW",IF(ISNA(VLOOKUP(E301,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H301" s="24" t="str">
+        <f>IF(J301&lt;&gt;1,"",IF(I301="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I301" s="25" t="str">
+        <f>IF(OR(E301="",E301="!!!",F301="NEW"),"",INDEX(B300:B$2,-1+SUMPRODUCT(MAX(ROW(E300:E$2)*(E301=E300:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J301" s="25" t="str">
+        <f>IF(OR(E301="",E301="!!!",F301="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E301)*(E301=E$2:E301)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E300)*(E2=E$1:E300))))))</f>
+        <v> </v>
+      </c>
+      <c r="K301" s="25" t="str">
+        <f>IF(OR(E301="",E301="!!!",F301="NEW"),"",INDEX(J$1:J300,SUMPRODUCT(MAX(ROW(E$1:E300)*(E301=E$1:E300)))))</f>
+        <v> </v>
+      </c>
+      <c r="L301" s="26"/>
     </row>
     <row r="302" spans="1:12">
       <c r="A302" s="20" t="s">
-        <v>264</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E302" s="21">
+        <f>IF(D302="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F302" s="22" t="str">
+        <f>IF(OR(E302="",E302="!!!"),"",IF(NOT(ISNA(VLOOKUP(E302,E$1:E301,1,FALSE()))),"OLD",IF(AND(E302&lt;&gt;"",E302&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G302" s="23" t="str">
+        <f>IF(OR(E302="",E302="!!!"),"",IF(OR(J302=0,AND(J302=1,K302=1),AND(J302=1,I302="SBJ"),AND(J302=1,I302=0)),"?IN_FOCUS",IF(J302&lt;=2,"?ACTIVATED",IF(J302&lt;&gt;"","?FAMILIAR",IF(F302="NEW",IF(ISNA(VLOOKUP(E302,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H302" s="24" t="str">
+        <f>IF(J302&lt;&gt;1,"",IF(I302="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I302" s="25" t="str">
+        <f>IF(OR(E302="",E302="!!!",F302="NEW"),"",INDEX(B301:B$2,-1+SUMPRODUCT(MAX(ROW(E301:E$2)*(E302=E301:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J302" s="25" t="str">
+        <f>IF(OR(E302="",E302="!!!",F302="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E302)*(E302=E$2:E302)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E301)*(E2=E$1:E301))))))</f>
+        <v> </v>
+      </c>
+      <c r="K302" s="25" t="str">
+        <f>IF(OR(E302="",E302="!!!",F302="NEW"),"",INDEX(J$1:J301,SUMPRODUCT(MAX(ROW(E$1:E301)*(E302=E$1:E301)))))</f>
+        <v> </v>
+      </c>
+      <c r="L302" s="26"/>
     </row>
     <row r="303" spans="1:12">
-      <c r="A303" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B303" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C303" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D303" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E303" s="21">
-        <f>IF(D303="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F303" s="22" t="str">
-        <f>IF(OR(E303="",E303="!!!"),"",IF(NOT(ISNA(VLOOKUP(E303,E$1:E302,1,FALSE()))),"OLD",IF(AND(E303&lt;&gt;"",E303&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G303" s="23" t="str">
-        <f>IF(OR(E303="",E303="!!!"),"",IF(OR(J303=0,AND(J303=1,K303=1),AND(J303=1,I303="SBJ"),AND(J303=1,I303=0)),"?IN_FOCUS",IF(J303&lt;=2,"?ACTIVATED",IF(J303&lt;&gt;"","?FAMILIAR",IF(F303="NEW",IF(ISNA(VLOOKUP(E303,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H303" s="24" t="str">
-        <f>IF(J303&lt;&gt;1,"",IF(I303="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I303" s="25" t="str">
-        <f>IF(OR(E303="",E303="!!!",F303="NEW"),"",INDEX(B302:B$2,-1+SUMPRODUCT(MAX(ROW(E302:E$2)*(E303=E302:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J303" s="25" t="str">
-        <f>IF(OR(E303="",E303="!!!",F303="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E303)*(E303=E$2:E303)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E302)*(E2=E$1:E302))))))</f>
-        <v> </v>
-      </c>
-      <c r="K303" s="25" t="str">
-        <f>IF(OR(E303="",E303="!!!",F303="NEW"),"",INDEX(J$1:J302,SUMPRODUCT(MAX(ROW(E$1:E302)*(E303=E$1:E302)))))</f>
-        <v> </v>
-      </c>
-      <c r="L303" s="26"/>
+      <c r="A303" s="20"/>
     </row>
     <row r="304" spans="1:12">
       <c r="A304" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="E304" s="21">
-        <f>IF(D304="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F304" s="22" t="str">
-        <f>IF(OR(E304="",E304="!!!"),"",IF(NOT(ISNA(VLOOKUP(E304,E$1:E303,1,FALSE()))),"OLD",IF(AND(E304&lt;&gt;"",E304&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G304" s="23" t="str">
-        <f>IF(OR(E304="",E304="!!!"),"",IF(OR(J304=0,AND(J304=1,K304=1),AND(J304=1,I304="SBJ"),AND(J304=1,I304=0)),"?IN_FOCUS",IF(J304&lt;=2,"?ACTIVATED",IF(J304&lt;&gt;"","?FAMILIAR",IF(F304="NEW",IF(ISNA(VLOOKUP(E304,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H304" s="24" t="str">
-        <f>IF(J304&lt;&gt;1,"",IF(I304="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I304" s="25" t="str">
-        <f>IF(OR(E304="",E304="!!!",F304="NEW"),"",INDEX(B303:B$2,-1+SUMPRODUCT(MAX(ROW(E303:E$2)*(E304=E303:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J304" s="25" t="str">
-        <f>IF(OR(E304="",E304="!!!",F304="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E304)*(E304=E$2:E304)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E303)*(E2=E$1:E303))))))</f>
-        <v> </v>
-      </c>
-      <c r="K304" s="25" t="str">
-        <f>IF(OR(E304="",E304="!!!",F304="NEW"),"",INDEX(J$1:J303,SUMPRODUCT(MAX(ROW(E$1:E303)*(E304=E$1:E303)))))</f>
-        <v> </v>
-      </c>
-      <c r="L304" s="26"/>
+        <v>268</v>
+      </c>
     </row>
     <row r="305" spans="1:12">
       <c r="A305" s="20" t="s">
-        <v>132</v>
+        <v>191</v>
+      </c>
+      <c r="B305" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C305" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D305" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E305" s="21">
         <f>IF(D305="?OLD","!!!","")</f>
@@ -12440,7 +12423,7 @@
     </row>
     <row r="306" spans="1:12">
       <c r="A306" s="20" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="E306" s="21">
         <f>IF(D306="?OLD","!!!","")</f>
@@ -12474,7 +12457,7 @@
     </row>
     <row r="307" spans="1:12">
       <c r="A307" s="20" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E307" s="21">
         <f>IF(D307="?OLD","!!!","")</f>
@@ -12508,16 +12491,7 @@
     </row>
     <row r="308" spans="1:12">
       <c r="A308" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B308" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C308" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D308" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E308" s="21">
         <f>IF(D308="?OLD","!!!","")</f>
@@ -12553,9 +12527,6 @@
       <c r="A309" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B309" s="27" t="s">
-        <v>139</v>
-      </c>
       <c r="E309" s="21">
         <f>IF(D309="?OLD","!!!","")</f>
         <v/>
@@ -12588,13 +12559,16 @@
     </row>
     <row r="310" spans="1:12">
       <c r="A310" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B310" s="27" t="s">
         <v>140</v>
-      </c>
-      <c r="B310" s="27" t="s">
-        <v>139</v>
       </c>
       <c r="C310" s="27" t="s">
         <v>141</v>
+      </c>
+      <c r="D310" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E310" s="21">
         <f>IF(D310="?OLD","!!!","")</f>
@@ -12630,6 +12604,9 @@
       <c r="A311" s="20" t="s">
         <v>142</v>
       </c>
+      <c r="B311" s="27" t="s">
+        <v>143</v>
+      </c>
       <c r="E311" s="21">
         <f>IF(D311="?OLD","!!!","")</f>
         <v/>
@@ -12662,7 +12639,13 @@
     </row>
     <row r="312" spans="1:12">
       <c r="A312" s="20" t="s">
-        <v>265</v>
+        <v>144</v>
+      </c>
+      <c r="B312" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C312" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="E312" s="21">
         <f>IF(D312="?OLD","!!!","")</f>
@@ -12696,7 +12679,7 @@
     </row>
     <row r="313" spans="1:12">
       <c r="A313" s="20" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="E313" s="21">
         <f>IF(D313="?OLD","!!!","")</f>
@@ -12730,10 +12713,7 @@
     </row>
     <row r="314" spans="1:12">
       <c r="A314" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="B314" s="27" t="s">
-        <v>136</v>
+        <v>269</v>
       </c>
       <c r="E314" s="21">
         <f>IF(D314="?OLD","!!!","")</f>
@@ -12767,7 +12747,7 @@
     </row>
     <row r="315" spans="1:12">
       <c r="A315" s="20" t="s">
-        <v>266</v>
+        <v>108</v>
       </c>
       <c r="E315" s="21">
         <f>IF(D315="?OLD","!!!","")</f>
@@ -12801,7 +12781,10 @@
     </row>
     <row r="316" spans="1:12">
       <c r="A316" s="20" t="s">
-        <v>267</v>
+        <v>109</v>
+      </c>
+      <c r="B316" s="27" t="s">
+        <v>140</v>
       </c>
       <c r="E316" s="21">
         <f>IF(D316="?OLD","!!!","")</f>
@@ -12835,13 +12818,7 @@
     </row>
     <row r="317" spans="1:12">
       <c r="A317" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B317" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C317" s="27" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="E317" s="21">
         <f>IF(D317="?OLD","!!!","")</f>
@@ -12875,7 +12852,7 @@
     </row>
     <row r="318" spans="1:12">
       <c r="A318" s="20" t="s">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c r="E318" s="21">
         <f>IF(D318="?OLD","!!!","")</f>
@@ -12909,7 +12886,13 @@
     </row>
     <row r="319" spans="1:12">
       <c r="A319" s="20" t="s">
-        <v>146</v>
+        <v>133</v>
+      </c>
+      <c r="B319" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C319" s="27" t="s">
+        <v>205</v>
       </c>
       <c r="E319" s="21">
         <f>IF(D319="?OLD","!!!","")</f>
@@ -12943,7 +12926,7 @@
     </row>
     <row r="320" spans="1:12">
       <c r="A320" s="20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E320" s="21">
         <f>IF(D320="?OLD","!!!","")</f>
@@ -12977,7 +12960,7 @@
     </row>
     <row r="321" spans="1:12">
       <c r="A321" s="20" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E321" s="21">
         <f>IF(D321="?OLD","!!!","")</f>
@@ -13010,93 +12993,93 @@
       <c r="L321" s="26"/>
     </row>
     <row r="322" spans="1:12">
-      <c r="A322" s="20"/>
+      <c r="A322" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E322" s="21">
+        <f>IF(D322="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F322" s="22" t="str">
+        <f>IF(OR(E322="",E322="!!!"),"",IF(NOT(ISNA(VLOOKUP(E322,E$1:E321,1,FALSE()))),"OLD",IF(AND(E322&lt;&gt;"",E322&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G322" s="23" t="str">
+        <f>IF(OR(E322="",E322="!!!"),"",IF(OR(J322=0,AND(J322=1,K322=1),AND(J322=1,I322="SBJ"),AND(J322=1,I322=0)),"?IN_FOCUS",IF(J322&lt;=2,"?ACTIVATED",IF(J322&lt;&gt;"","?FAMILIAR",IF(F322="NEW",IF(ISNA(VLOOKUP(E322,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H322" s="24" t="str">
+        <f>IF(J322&lt;&gt;1,"",IF(I322="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I322" s="25" t="str">
+        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",INDEX(B321:B$2,-1+SUMPRODUCT(MAX(ROW(E321:E$2)*(E322=E321:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J322" s="25" t="str">
+        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E322)*(E322=E$2:E322)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E321)*(E2=E$1:E321))))))</f>
+        <v> </v>
+      </c>
+      <c r="K322" s="25" t="str">
+        <f>IF(OR(E322="",E322="!!!",F322="NEW"),"",INDEX(J$1:J321,SUMPRODUCT(MAX(ROW(E$1:E321)*(E322=E$1:E321)))))</f>
+        <v> </v>
+      </c>
+      <c r="L322" s="26"/>
     </row>
     <row r="323" spans="1:12">
       <c r="A323" s="20" t="s">
-        <v>268</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E323" s="21">
+        <f>IF(D323="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F323" s="22" t="str">
+        <f>IF(OR(E323="",E323="!!!"),"",IF(NOT(ISNA(VLOOKUP(E323,E$1:E322,1,FALSE()))),"OLD",IF(AND(E323&lt;&gt;"",E323&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G323" s="23" t="str">
+        <f>IF(OR(E323="",E323="!!!"),"",IF(OR(J323=0,AND(J323=1,K323=1),AND(J323=1,I323="SBJ"),AND(J323=1,I323=0)),"?IN_FOCUS",IF(J323&lt;=2,"?ACTIVATED",IF(J323&lt;&gt;"","?FAMILIAR",IF(F323="NEW",IF(ISNA(VLOOKUP(E323,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H323" s="24" t="str">
+        <f>IF(J323&lt;&gt;1,"",IF(I323="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I323" s="25" t="str">
+        <f>IF(OR(E323="",E323="!!!",F323="NEW"),"",INDEX(B322:B$2,-1+SUMPRODUCT(MAX(ROW(E322:E$2)*(E323=E322:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J323" s="25" t="str">
+        <f>IF(OR(E323="",E323="!!!",F323="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E323)*(E323=E$2:E323)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E322)*(E2=E$1:E322))))))</f>
+        <v> </v>
+      </c>
+      <c r="K323" s="25" t="str">
+        <f>IF(OR(E323="",E323="!!!",F323="NEW"),"",INDEX(J$1:J322,SUMPRODUCT(MAX(ROW(E$1:E322)*(E323=E$1:E322)))))</f>
+        <v> </v>
+      </c>
+      <c r="L323" s="26"/>
     </row>
     <row r="324" spans="1:12">
-      <c r="A324" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B324" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C324" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D324" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E324" s="21">
-        <f>IF(D324="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F324" s="22" t="str">
-        <f>IF(OR(E324="",E324="!!!"),"",IF(NOT(ISNA(VLOOKUP(E324,E$1:E323,1,FALSE()))),"OLD",IF(AND(E324&lt;&gt;"",E324&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G324" s="23" t="str">
-        <f>IF(OR(E324="",E324="!!!"),"",IF(OR(J324=0,AND(J324=1,K324=1),AND(J324=1,I324="SBJ"),AND(J324=1,I324=0)),"?IN_FOCUS",IF(J324&lt;=2,"?ACTIVATED",IF(J324&lt;&gt;"","?FAMILIAR",IF(F324="NEW",IF(ISNA(VLOOKUP(E324,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H324" s="24" t="str">
-        <f>IF(J324&lt;&gt;1,"",IF(I324="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I324" s="25" t="str">
-        <f>IF(OR(E324="",E324="!!!",F324="NEW"),"",INDEX(B323:B$2,-1+SUMPRODUCT(MAX(ROW(E323:E$2)*(E324=E323:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J324" s="25" t="str">
-        <f>IF(OR(E324="",E324="!!!",F324="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E324)*(E324=E$2:E324)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E323)*(E2=E$1:E323))))))</f>
-        <v> </v>
-      </c>
-      <c r="K324" s="25" t="str">
-        <f>IF(OR(E324="",E324="!!!",F324="NEW"),"",INDEX(J$1:J323,SUMPRODUCT(MAX(ROW(E$1:E323)*(E324=E$1:E323)))))</f>
-        <v> </v>
-      </c>
-      <c r="L324" s="26"/>
+      <c r="A324" s="20"/>
     </row>
     <row r="325" spans="1:12">
       <c r="A325" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="E325" s="21">
-        <f>IF(D325="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F325" s="22" t="str">
-        <f>IF(OR(E325="",E325="!!!"),"",IF(NOT(ISNA(VLOOKUP(E325,E$1:E324,1,FALSE()))),"OLD",IF(AND(E325&lt;&gt;"",E325&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G325" s="23" t="str">
-        <f>IF(OR(E325="",E325="!!!"),"",IF(OR(J325=0,AND(J325=1,K325=1),AND(J325=1,I325="SBJ"),AND(J325=1,I325=0)),"?IN_FOCUS",IF(J325&lt;=2,"?ACTIVATED",IF(J325&lt;&gt;"","?FAMILIAR",IF(F325="NEW",IF(ISNA(VLOOKUP(E325,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H325" s="24" t="str">
-        <f>IF(J325&lt;&gt;1,"",IF(I325="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I325" s="25" t="str">
-        <f>IF(OR(E325="",E325="!!!",F325="NEW"),"",INDEX(B324:B$2,-1+SUMPRODUCT(MAX(ROW(E324:E$2)*(E325=E324:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J325" s="25" t="str">
-        <f>IF(OR(E325="",E325="!!!",F325="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E325)*(E325=E$2:E325)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E324)*(E2=E$1:E324))))))</f>
-        <v> </v>
-      </c>
-      <c r="K325" s="25" t="str">
-        <f>IF(OR(E325="",E325="!!!",F325="NEW"),"",INDEX(J$1:J324,SUMPRODUCT(MAX(ROW(E$1:E324)*(E325=E$1:E324)))))</f>
-        <v> </v>
-      </c>
-      <c r="L325" s="26"/>
+        <v>272</v>
+      </c>
     </row>
     <row r="326" spans="1:12">
       <c r="A326" s="20" t="s">
-        <v>219</v>
+        <v>263</v>
+      </c>
+      <c r="B326" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C326" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D326" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E326" s="21">
         <f>IF(D326="?OLD","!!!","")</f>
@@ -13130,7 +13113,7 @@
     </row>
     <row r="327" spans="1:12">
       <c r="A327" s="20" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E327" s="21">
         <f>IF(D327="?OLD","!!!","")</f>
@@ -13164,13 +13147,7 @@
     </row>
     <row r="328" spans="1:12">
       <c r="A328" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="B328" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C328" s="27" t="s">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="E328" s="21">
         <f>IF(D328="?OLD","!!!","")</f>
@@ -13204,7 +13181,7 @@
     </row>
     <row r="329" spans="1:12">
       <c r="A329" s="20" t="s">
-        <v>175</v>
+        <v>274</v>
       </c>
       <c r="E329" s="21">
         <f>IF(D329="?OLD","!!!","")</f>
@@ -13238,7 +13215,13 @@
     </row>
     <row r="330" spans="1:12">
       <c r="A330" s="20" t="s">
-        <v>272</v>
+        <v>275</v>
+      </c>
+      <c r="B330" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C330" s="27" t="s">
+        <v>128</v>
       </c>
       <c r="E330" s="21">
         <f>IF(D330="?OLD","!!!","")</f>
@@ -13272,7 +13255,7 @@
     </row>
     <row r="331" spans="1:12">
       <c r="A331" s="20" t="s">
-        <v>273</v>
+        <v>178</v>
       </c>
       <c r="E331" s="21">
         <f>IF(D331="?OLD","!!!","")</f>
@@ -13306,13 +13289,7 @@
     </row>
     <row r="332" spans="1:12">
       <c r="A332" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="B332" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C332" s="27" t="s">
-        <v>124</v>
+        <v>276</v>
       </c>
       <c r="E332" s="21">
         <f>IF(D332="?OLD","!!!","")</f>
@@ -13346,7 +13323,7 @@
     </row>
     <row r="333" spans="1:12">
       <c r="A333" s="20" t="s">
-        <v>125</v>
+        <v>277</v>
       </c>
       <c r="E333" s="21">
         <f>IF(D333="?OLD","!!!","")</f>
@@ -13379,11 +13356,48 @@
       <c r="L333" s="26"/>
     </row>
     <row r="334" spans="1:12">
-      <c r="A334" s="20"/>
+      <c r="A334" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="B334" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C334" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E334" s="21">
+        <f>IF(D334="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F334" s="22" t="str">
+        <f>IF(OR(E334="",E334="!!!"),"",IF(NOT(ISNA(VLOOKUP(E334,E$1:E333,1,FALSE()))),"OLD",IF(AND(E334&lt;&gt;"",E334&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G334" s="23" t="str">
+        <f>IF(OR(E334="",E334="!!!"),"",IF(OR(J334=0,AND(J334=1,K334=1),AND(J334=1,I334="SBJ"),AND(J334=1,I334=0)),"?IN_FOCUS",IF(J334&lt;=2,"?ACTIVATED",IF(J334&lt;&gt;"","?FAMILIAR",IF(F334="NEW",IF(ISNA(VLOOKUP(E334,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H334" s="24" t="str">
+        <f>IF(J334&lt;&gt;1,"",IF(I334="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I334" s="25" t="str">
+        <f>IF(OR(E334="",E334="!!!",F334="NEW"),"",INDEX(B333:B$2,-1+SUMPRODUCT(MAX(ROW(E333:E$2)*(E334=E333:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J334" s="25" t="str">
+        <f>IF(OR(E334="",E334="!!!",F334="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E334)*(E334=E$2:E334)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E333)*(E2=E$1:E333))))))</f>
+        <v> </v>
+      </c>
+      <c r="K334" s="25" t="str">
+        <f>IF(OR(E334="",E334="!!!",F334="NEW"),"",INDEX(J$1:J333,SUMPRODUCT(MAX(ROW(E$1:E333)*(E334=E$1:E333)))))</f>
+        <v> </v>
+      </c>
+      <c r="L334" s="26"/>
     </row>
     <row r="335" spans="1:12">
       <c r="A335" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E335" s="21">
         <f>IF(D335="?OLD","!!!","")</f>
@@ -13416,13 +13430,11 @@
       <c r="L335" s="26"/>
     </row>
     <row r="336" spans="1:12">
-      <c r="A336" s="20" t="s">
-        <v>275</v>
-      </c>
+      <c r="A336" s="20"/>
     </row>
     <row r="337" spans="1:12">
       <c r="A337" s="20" t="s">
-        <v>276</v>
+        <v>130</v>
       </c>
       <c r="E337" s="21">
         <f>IF(D337="?OLD","!!!","")</f>
@@ -13456,47 +13468,12 @@
     </row>
     <row r="338" spans="1:12">
       <c r="A338" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="B338" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C338" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="E338" s="21">
-        <f>IF(D338="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F338" s="22" t="str">
-        <f>IF(OR(E338="",E338="!!!"),"",IF(NOT(ISNA(VLOOKUP(E338,E$1:E337,1,FALSE()))),"OLD",IF(AND(E338&lt;&gt;"",E338&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G338" s="23" t="str">
-        <f>IF(OR(E338="",E338="!!!"),"",IF(OR(J338=0,AND(J338=1,K338=1),AND(J338=1,I338="SBJ"),AND(J338=1,I338=0)),"?IN_FOCUS",IF(J338&lt;=2,"?ACTIVATED",IF(J338&lt;&gt;"","?FAMILIAR",IF(F338="NEW",IF(ISNA(VLOOKUP(E338,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H338" s="24" t="str">
-        <f>IF(J338&lt;&gt;1,"",IF(I338="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I338" s="25" t="str">
-        <f>IF(OR(E338="",E338="!!!",F338="NEW"),"",INDEX(B337:B$2,-1+SUMPRODUCT(MAX(ROW(E337:E$2)*(E338=E337:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J338" s="25" t="str">
-        <f>IF(OR(E338="",E338="!!!",F338="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E338)*(E338=E$2:E338)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E337)*(E2=E$1:E337))))))</f>
-        <v> </v>
-      </c>
-      <c r="K338" s="25" t="str">
-        <f>IF(OR(E338="",E338="!!!",F338="NEW"),"",INDEX(J$1:J337,SUMPRODUCT(MAX(ROW(E$1:E337)*(E338=E$1:E337)))))</f>
-        <v> </v>
-      </c>
-      <c r="L338" s="26"/>
+        <v>279</v>
+      </c>
     </row>
     <row r="339" spans="1:12">
       <c r="A339" s="20" t="s">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="E339" s="21">
         <f>IF(D339="?OLD","!!!","")</f>
@@ -13530,7 +13507,13 @@
     </row>
     <row r="340" spans="1:12">
       <c r="A340" s="20" t="s">
-        <v>278</v>
+        <v>281</v>
+      </c>
+      <c r="B340" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="C340" s="27" t="s">
+        <v>205</v>
       </c>
       <c r="E340" s="21">
         <f>IF(D340="?OLD","!!!","")</f>
@@ -13564,13 +13547,7 @@
     </row>
     <row r="341" spans="1:12">
       <c r="A341" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B341" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C341" s="27" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="E341" s="21">
         <f>IF(D341="?OLD","!!!","")</f>
@@ -13604,7 +13581,7 @@
     </row>
     <row r="342" spans="1:12">
       <c r="A342" s="20" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E342" s="21">
         <f>IF(D342="?OLD","!!!","")</f>
@@ -13638,7 +13615,13 @@
     </row>
     <row r="343" spans="1:12">
       <c r="A343" s="20" t="s">
-        <v>280</v>
+        <v>230</v>
+      </c>
+      <c r="B343" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C343" s="27" t="s">
+        <v>205</v>
       </c>
       <c r="E343" s="21">
         <f>IF(D343="?OLD","!!!","")</f>
@@ -13672,7 +13655,7 @@
     </row>
     <row r="344" spans="1:12">
       <c r="A344" s="20" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E344" s="21">
         <f>IF(D344="?OLD","!!!","")</f>
@@ -13706,16 +13689,7 @@
     </row>
     <row r="345" spans="1:12">
       <c r="A345" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="B345" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C345" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D345" s="27" t="s">
-        <v>95</v>
+        <v>284</v>
       </c>
       <c r="E345" s="21">
         <f>IF(D345="?OLD","!!!","")</f>
@@ -13749,7 +13723,7 @@
     </row>
     <row r="346" spans="1:12">
       <c r="A346" s="20" t="s">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="E346" s="21">
         <f>IF(D346="?OLD","!!!","")</f>
@@ -13783,16 +13757,16 @@
     </row>
     <row r="347" spans="1:12">
       <c r="A347" s="20" t="s">
-        <v>281</v>
+        <v>155</v>
       </c>
       <c r="B347" s="27" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="C347" s="27" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="D347" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E347" s="21">
         <f>IF(D347="?OLD","!!!","")</f>
@@ -13826,7 +13800,7 @@
     </row>
     <row r="348" spans="1:12">
       <c r="A348" s="20" t="s">
-        <v>282</v>
+        <v>108</v>
       </c>
       <c r="E348" s="21">
         <f>IF(D348="?OLD","!!!","")</f>
@@ -13860,13 +13834,16 @@
     </row>
     <row r="349" spans="1:12">
       <c r="A349" s="20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B349" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C349" s="27" t="s">
-        <v>141</v>
+        <v>111</v>
+      </c>
+      <c r="D349" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E349" s="21">
         <f>IF(D349="?OLD","!!!","")</f>
@@ -13900,7 +13877,7 @@
     </row>
     <row r="350" spans="1:12">
       <c r="A350" s="20" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E350" s="21">
         <f>IF(D350="?OLD","!!!","")</f>
@@ -13934,7 +13911,13 @@
     </row>
     <row r="351" spans="1:12">
       <c r="A351" s="20" t="s">
-        <v>284</v>
+        <v>287</v>
+      </c>
+      <c r="B351" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C351" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="E351" s="21">
         <f>IF(D351="?OLD","!!!","")</f>
@@ -13968,7 +13951,7 @@
     </row>
     <row r="352" spans="1:12">
       <c r="A352" s="20" t="s">
-        <v>105</v>
+        <v>283</v>
       </c>
       <c r="E352" s="21">
         <f>IF(D352="?OLD","!!!","")</f>
@@ -14002,16 +13985,7 @@
     </row>
     <row r="353" spans="1:12">
       <c r="A353" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="B353" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="C353" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D353" s="27" t="s">
-        <v>95</v>
+        <v>288</v>
       </c>
       <c r="E353" s="21">
         <f>IF(D353="?OLD","!!!","")</f>
@@ -14045,7 +14019,7 @@
     </row>
     <row r="354" spans="1:12">
       <c r="A354" s="20" t="s">
-        <v>222</v>
+        <v>108</v>
       </c>
       <c r="E354" s="21">
         <f>IF(D354="?OLD","!!!","")</f>
@@ -14082,13 +14056,13 @@
         <v>285</v>
       </c>
       <c r="B355" s="27" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C355" s="27" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D355" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E355" s="21">
         <f>IF(D355="?OLD","!!!","")</f>
@@ -14122,7 +14096,7 @@
     </row>
     <row r="356" spans="1:12">
       <c r="A356" s="20" t="s">
-        <v>286</v>
+        <v>226</v>
       </c>
       <c r="E356" s="21">
         <f>IF(D356="?OLD","!!!","")</f>
@@ -14156,7 +14130,16 @@
     </row>
     <row r="357" spans="1:12">
       <c r="A357" s="20" t="s">
-        <v>105</v>
+        <v>289</v>
+      </c>
+      <c r="B357" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C357" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D357" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E357" s="21">
         <f>IF(D357="?OLD","!!!","")</f>
@@ -14190,7 +14173,7 @@
     </row>
     <row r="358" spans="1:12">
       <c r="A358" s="20" t="s">
-        <v>148</v>
+        <v>290</v>
       </c>
       <c r="E358" s="21">
         <f>IF(D358="?OLD","!!!","")</f>
@@ -14224,7 +14207,7 @@
     </row>
     <row r="359" spans="1:12">
       <c r="A359" s="20" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E359" s="21">
         <f>IF(D359="?OLD","!!!","")</f>
@@ -14258,16 +14241,7 @@
     </row>
     <row r="360" spans="1:12">
       <c r="A360" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B360" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C360" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D360" s="27" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E360" s="21">
         <f>IF(D360="?OLD","!!!","")</f>
@@ -14301,7 +14275,7 @@
     </row>
     <row r="361" spans="1:12">
       <c r="A361" s="20" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="E361" s="21">
         <f>IF(D361="?OLD","!!!","")</f>
@@ -14335,7 +14309,16 @@
     </row>
     <row r="362" spans="1:12">
       <c r="A362" s="20" t="s">
-        <v>125</v>
+        <v>191</v>
+      </c>
+      <c r="B362" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C362" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D362" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E362" s="21">
         <f>IF(D362="?OLD","!!!","")</f>
@@ -14368,93 +14351,93 @@
       <c r="L362" s="26"/>
     </row>
     <row r="363" spans="1:12">
-      <c r="A363" s="20"/>
+      <c r="A363" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E363" s="21">
+        <f>IF(D363="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F363" s="22" t="str">
+        <f>IF(OR(E363="",E363="!!!"),"",IF(NOT(ISNA(VLOOKUP(E363,E$1:E362,1,FALSE()))),"OLD",IF(AND(E363&lt;&gt;"",E363&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G363" s="23" t="str">
+        <f>IF(OR(E363="",E363="!!!"),"",IF(OR(J363=0,AND(J363=1,K363=1),AND(J363=1,I363="SBJ"),AND(J363=1,I363=0)),"?IN_FOCUS",IF(J363&lt;=2,"?ACTIVATED",IF(J363&lt;&gt;"","?FAMILIAR",IF(F363="NEW",IF(ISNA(VLOOKUP(E363,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H363" s="24" t="str">
+        <f>IF(J363&lt;&gt;1,"",IF(I363="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I363" s="25" t="str">
+        <f>IF(OR(E363="",E363="!!!",F363="NEW"),"",INDEX(B362:B$2,-1+SUMPRODUCT(MAX(ROW(E362:E$2)*(E363=E362:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J363" s="25" t="str">
+        <f>IF(OR(E363="",E363="!!!",F363="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E363)*(E363=E$2:E363)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E362)*(E2=E$1:E362))))))</f>
+        <v> </v>
+      </c>
+      <c r="K363" s="25" t="str">
+        <f>IF(OR(E363="",E363="!!!",F363="NEW"),"",INDEX(J$1:J362,SUMPRODUCT(MAX(ROW(E$1:E362)*(E363=E$1:E362)))))</f>
+        <v> </v>
+      </c>
+      <c r="L363" s="26"/>
     </row>
     <row r="364" spans="1:12">
       <c r="A364" s="20" t="s">
-        <v>287</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E364" s="21">
+        <f>IF(D364="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F364" s="22" t="str">
+        <f>IF(OR(E364="",E364="!!!"),"",IF(NOT(ISNA(VLOOKUP(E364,E$1:E363,1,FALSE()))),"OLD",IF(AND(E364&lt;&gt;"",E364&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G364" s="23" t="str">
+        <f>IF(OR(E364="",E364="!!!"),"",IF(OR(J364=0,AND(J364=1,K364=1),AND(J364=1,I364="SBJ"),AND(J364=1,I364=0)),"?IN_FOCUS",IF(J364&lt;=2,"?ACTIVATED",IF(J364&lt;&gt;"","?FAMILIAR",IF(F364="NEW",IF(ISNA(VLOOKUP(E364,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H364" s="24" t="str">
+        <f>IF(J364&lt;&gt;1,"",IF(I364="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I364" s="25" t="str">
+        <f>IF(OR(E364="",E364="!!!",F364="NEW"),"",INDEX(B363:B$2,-1+SUMPRODUCT(MAX(ROW(E363:E$2)*(E364=E363:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J364" s="25" t="str">
+        <f>IF(OR(E364="",E364="!!!",F364="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E364)*(E364=E$2:E364)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E363)*(E2=E$1:E363))))))</f>
+        <v> </v>
+      </c>
+      <c r="K364" s="25" t="str">
+        <f>IF(OR(E364="",E364="!!!",F364="NEW"),"",INDEX(J$1:J363,SUMPRODUCT(MAX(ROW(E$1:E363)*(E364=E$1:E363)))))</f>
+        <v> </v>
+      </c>
+      <c r="L364" s="26"/>
     </row>
     <row r="365" spans="1:12">
-      <c r="A365" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B365" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C365" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D365" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E365" s="21">
-        <f>IF(D365="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F365" s="22" t="str">
-        <f>IF(OR(E365="",E365="!!!"),"",IF(NOT(ISNA(VLOOKUP(E365,E$1:E364,1,FALSE()))),"OLD",IF(AND(E365&lt;&gt;"",E365&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G365" s="23" t="str">
-        <f>IF(OR(E365="",E365="!!!"),"",IF(OR(J365=0,AND(J365=1,K365=1),AND(J365=1,I365="SBJ"),AND(J365=1,I365=0)),"?IN_FOCUS",IF(J365&lt;=2,"?ACTIVATED",IF(J365&lt;&gt;"","?FAMILIAR",IF(F365="NEW",IF(ISNA(VLOOKUP(E365,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H365" s="24" t="str">
-        <f>IF(J365&lt;&gt;1,"",IF(I365="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I365" s="25" t="str">
-        <f>IF(OR(E365="",E365="!!!",F365="NEW"),"",INDEX(B364:B$2,-1+SUMPRODUCT(MAX(ROW(E364:E$2)*(E365=E364:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J365" s="25" t="str">
-        <f>IF(OR(E365="",E365="!!!",F365="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E365)*(E365=E$2:E365)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E364)*(E2=E$1:E364))))))</f>
-        <v> </v>
-      </c>
-      <c r="K365" s="25" t="str">
-        <f>IF(OR(E365="",E365="!!!",F365="NEW"),"",INDEX(J$1:J364,SUMPRODUCT(MAX(ROW(E$1:E364)*(E365=E$1:E364)))))</f>
-        <v> </v>
-      </c>
-      <c r="L365" s="26"/>
+      <c r="A365" s="20"/>
     </row>
     <row r="366" spans="1:12">
       <c r="A366" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="E366" s="21">
-        <f>IF(D366="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F366" s="22" t="str">
-        <f>IF(OR(E366="",E366="!!!"),"",IF(NOT(ISNA(VLOOKUP(E366,E$1:E365,1,FALSE()))),"OLD",IF(AND(E366&lt;&gt;"",E366&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G366" s="23" t="str">
-        <f>IF(OR(E366="",E366="!!!"),"",IF(OR(J366=0,AND(J366=1,K366=1),AND(J366=1,I366="SBJ"),AND(J366=1,I366=0)),"?IN_FOCUS",IF(J366&lt;=2,"?ACTIVATED",IF(J366&lt;&gt;"","?FAMILIAR",IF(F366="NEW",IF(ISNA(VLOOKUP(E366,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H366" s="24" t="str">
-        <f>IF(J366&lt;&gt;1,"",IF(I366="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I366" s="25" t="str">
-        <f>IF(OR(E366="",E366="!!!",F366="NEW"),"",INDEX(B365:B$2,-1+SUMPRODUCT(MAX(ROW(E365:E$2)*(E366=E365:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J366" s="25" t="str">
-        <f>IF(OR(E366="",E366="!!!",F366="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E366)*(E366=E$2:E366)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E365)*(E2=E$1:E365))))))</f>
-        <v> </v>
-      </c>
-      <c r="K366" s="25" t="str">
-        <f>IF(OR(E366="",E366="!!!",F366="NEW"),"",INDEX(J$1:J365,SUMPRODUCT(MAX(ROW(E$1:E365)*(E366=E$1:E365)))))</f>
-        <v> </v>
-      </c>
-      <c r="L366" s="26"/>
+        <v>291</v>
+      </c>
     </row>
     <row r="367" spans="1:12">
       <c r="A367" s="20" t="s">
-        <v>289</v>
+        <v>263</v>
+      </c>
+      <c r="B367" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C367" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D367" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E367" s="21">
         <f>IF(D367="?OLD","!!!","")</f>
@@ -14488,7 +14471,7 @@
     </row>
     <row r="368" spans="1:12">
       <c r="A368" s="20" t="s">
-        <v>156</v>
+        <v>292</v>
       </c>
       <c r="E368" s="21">
         <f>IF(D368="?OLD","!!!","")</f>
@@ -14522,7 +14505,7 @@
     </row>
     <row r="369" spans="1:12">
       <c r="A369" s="20" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E369" s="21">
         <f>IF(D369="?OLD","!!!","")</f>
@@ -14556,13 +14539,7 @@
     </row>
     <row r="370" spans="1:12">
       <c r="A370" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="B370" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C370" s="27" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="E370" s="21">
         <f>IF(D370="?OLD","!!!","")</f>
@@ -14596,7 +14573,7 @@
     </row>
     <row r="371" spans="1:12">
       <c r="A371" s="20" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E371" s="21">
         <f>IF(D371="?OLD","!!!","")</f>
@@ -14630,13 +14607,13 @@
     </row>
     <row r="372" spans="1:12">
       <c r="A372" s="20" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B372" s="27" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="C372" s="27" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="E372" s="21">
         <f>IF(D372="?OLD","!!!","")</f>
@@ -14670,7 +14647,7 @@
     </row>
     <row r="373" spans="1:12">
       <c r="A373" s="20" t="s">
-        <v>63</v>
+        <v>295</v>
       </c>
       <c r="E373" s="21">
         <f>IF(D373="?OLD","!!!","")</f>
@@ -14704,7 +14681,13 @@
     </row>
     <row r="374" spans="1:12">
       <c r="A374" s="20" t="s">
-        <v>125</v>
+        <v>296</v>
+      </c>
+      <c r="B374" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C374" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="E374" s="21">
         <f>IF(D374="?OLD","!!!","")</f>
@@ -14737,93 +14720,93 @@
       <c r="L374" s="26"/>
     </row>
     <row r="375" spans="1:12">
-      <c r="A375" s="20"/>
+      <c r="A375" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E375" s="21">
+        <f>IF(D375="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F375" s="22" t="str">
+        <f>IF(OR(E375="",E375="!!!"),"",IF(NOT(ISNA(VLOOKUP(E375,E$1:E374,1,FALSE()))),"OLD",IF(AND(E375&lt;&gt;"",E375&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G375" s="23" t="str">
+        <f>IF(OR(E375="",E375="!!!"),"",IF(OR(J375=0,AND(J375=1,K375=1),AND(J375=1,I375="SBJ"),AND(J375=1,I375=0)),"?IN_FOCUS",IF(J375&lt;=2,"?ACTIVATED",IF(J375&lt;&gt;"","?FAMILIAR",IF(F375="NEW",IF(ISNA(VLOOKUP(E375,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H375" s="24" t="str">
+        <f>IF(J375&lt;&gt;1,"",IF(I375="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I375" s="25" t="str">
+        <f>IF(OR(E375="",E375="!!!",F375="NEW"),"",INDEX(B374:B$2,-1+SUMPRODUCT(MAX(ROW(E374:E$2)*(E375=E374:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J375" s="25" t="str">
+        <f>IF(OR(E375="",E375="!!!",F375="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E375)*(E375=E$2:E375)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E374)*(E2=E$1:E374))))))</f>
+        <v> </v>
+      </c>
+      <c r="K375" s="25" t="str">
+        <f>IF(OR(E375="",E375="!!!",F375="NEW"),"",INDEX(J$1:J374,SUMPRODUCT(MAX(ROW(E$1:E374)*(E375=E$1:E374)))))</f>
+        <v> </v>
+      </c>
+      <c r="L375" s="26"/>
     </row>
     <row r="376" spans="1:12">
       <c r="A376" s="20" t="s">
-        <v>293</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E376" s="21">
+        <f>IF(D376="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F376" s="22" t="str">
+        <f>IF(OR(E376="",E376="!!!"),"",IF(NOT(ISNA(VLOOKUP(E376,E$1:E375,1,FALSE()))),"OLD",IF(AND(E376&lt;&gt;"",E376&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G376" s="23" t="str">
+        <f>IF(OR(E376="",E376="!!!"),"",IF(OR(J376=0,AND(J376=1,K376=1),AND(J376=1,I376="SBJ"),AND(J376=1,I376=0)),"?IN_FOCUS",IF(J376&lt;=2,"?ACTIVATED",IF(J376&lt;&gt;"","?FAMILIAR",IF(F376="NEW",IF(ISNA(VLOOKUP(E376,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H376" s="24" t="str">
+        <f>IF(J376&lt;&gt;1,"",IF(I376="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I376" s="25" t="str">
+        <f>IF(OR(E376="",E376="!!!",F376="NEW"),"",INDEX(B375:B$2,-1+SUMPRODUCT(MAX(ROW(E375:E$2)*(E376=E375:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J376" s="25" t="str">
+        <f>IF(OR(E376="",E376="!!!",F376="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E376)*(E376=E$2:E376)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E375)*(E2=E$1:E375))))))</f>
+        <v> </v>
+      </c>
+      <c r="K376" s="25" t="str">
+        <f>IF(OR(E376="",E376="!!!",F376="NEW"),"",INDEX(J$1:J375,SUMPRODUCT(MAX(ROW(E$1:E375)*(E376=E$1:E375)))))</f>
+        <v> </v>
+      </c>
+      <c r="L376" s="26"/>
     </row>
     <row r="377" spans="1:12">
-      <c r="A377" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B377" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C377" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D377" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="E377" s="21">
-        <f>IF(D377="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F377" s="22" t="str">
-        <f>IF(OR(E377="",E377="!!!"),"",IF(NOT(ISNA(VLOOKUP(E377,E$1:E376,1,FALSE()))),"OLD",IF(AND(E377&lt;&gt;"",E377&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G377" s="23" t="str">
-        <f>IF(OR(E377="",E377="!!!"),"",IF(OR(J377=0,AND(J377=1,K377=1),AND(J377=1,I377="SBJ"),AND(J377=1,I377=0)),"?IN_FOCUS",IF(J377&lt;=2,"?ACTIVATED",IF(J377&lt;&gt;"","?FAMILIAR",IF(F377="NEW",IF(ISNA(VLOOKUP(E377,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H377" s="24" t="str">
-        <f>IF(J377&lt;&gt;1,"",IF(I377="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I377" s="25" t="str">
-        <f>IF(OR(E377="",E377="!!!",F377="NEW"),"",INDEX(B376:B$2,-1+SUMPRODUCT(MAX(ROW(E376:E$2)*(E377=E376:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J377" s="25" t="str">
-        <f>IF(OR(E377="",E377="!!!",F377="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E377)*(E377=E$2:E377)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E376)*(E2=E$1:E376))))))</f>
-        <v> </v>
-      </c>
-      <c r="K377" s="25" t="str">
-        <f>IF(OR(E377="",E377="!!!",F377="NEW"),"",INDEX(J$1:J376,SUMPRODUCT(MAX(ROW(E$1:E376)*(E377=E$1:E376)))))</f>
-        <v> </v>
-      </c>
-      <c r="L377" s="26"/>
+      <c r="A377" s="20"/>
     </row>
     <row r="378" spans="1:12">
       <c r="A378" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="E378" s="21">
-        <f>IF(D378="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F378" s="22" t="str">
-        <f>IF(OR(E378="",E378="!!!"),"",IF(NOT(ISNA(VLOOKUP(E378,E$1:E377,1,FALSE()))),"OLD",IF(AND(E378&lt;&gt;"",E378&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G378" s="23" t="str">
-        <f>IF(OR(E378="",E378="!!!"),"",IF(OR(J378=0,AND(J378=1,K378=1),AND(J378=1,I378="SBJ"),AND(J378=1,I378=0)),"?IN_FOCUS",IF(J378&lt;=2,"?ACTIVATED",IF(J378&lt;&gt;"","?FAMILIAR",IF(F378="NEW",IF(ISNA(VLOOKUP(E378,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H378" s="24" t="str">
-        <f>IF(J378&lt;&gt;1,"",IF(I378="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I378" s="25" t="str">
-        <f>IF(OR(E378="",E378="!!!",F378="NEW"),"",INDEX(B377:B$2,-1+SUMPRODUCT(MAX(ROW(E377:E$2)*(E378=E377:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J378" s="25" t="str">
-        <f>IF(OR(E378="",E378="!!!",F378="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E378)*(E378=E$2:E378)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E377)*(E2=E$1:E377))))))</f>
-        <v> </v>
-      </c>
-      <c r="K378" s="25" t="str">
-        <f>IF(OR(E378="",E378="!!!",F378="NEW"),"",INDEX(J$1:J377,SUMPRODUCT(MAX(ROW(E$1:E377)*(E378=E$1:E377)))))</f>
-        <v> </v>
-      </c>
-      <c r="L378" s="26"/>
+        <v>297</v>
+      </c>
     </row>
     <row r="379" spans="1:12">
       <c r="A379" s="20" t="s">
-        <v>106</v>
+        <v>263</v>
+      </c>
+      <c r="B379" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C379" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D379" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E379" s="21">
         <f>IF(D379="?OLD","!!!","")</f>
@@ -14857,16 +14840,7 @@
     </row>
     <row r="380" spans="1:12">
       <c r="A380" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="B380" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="C380" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D380" s="27" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="E380" s="21">
         <f>IF(D380="?OLD","!!!","")</f>
@@ -14900,7 +14874,7 @@
     </row>
     <row r="381" spans="1:12">
       <c r="A381" s="20" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E381" s="21">
         <f>IF(D381="?OLD","!!!","")</f>
@@ -14934,10 +14908,16 @@
     </row>
     <row r="382" spans="1:12">
       <c r="A382" s="20" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="B382" s="27" t="s">
-        <v>136</v>
+        <v>123</v>
+      </c>
+      <c r="C382" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D382" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E382" s="21">
         <f>IF(D382="?OLD","!!!","")</f>
@@ -14971,7 +14951,7 @@
     </row>
     <row r="383" spans="1:12">
       <c r="A383" s="20" t="s">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="E383" s="21">
         <f>IF(D383="?OLD","!!!","")</f>
@@ -15005,7 +14985,10 @@
     </row>
     <row r="384" spans="1:12">
       <c r="A384" s="20" t="s">
-        <v>118</v>
+        <v>109</v>
+      </c>
+      <c r="B384" s="27" t="s">
+        <v>140</v>
       </c>
       <c r="E384" s="21">
         <f>IF(D384="?OLD","!!!","")</f>
@@ -15039,16 +15022,7 @@
     </row>
     <row r="385" spans="1:12">
       <c r="A385" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="B385" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C385" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D385" s="27" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="E385" s="21">
         <f>IF(D385="?OLD","!!!","")</f>
@@ -15082,7 +15056,7 @@
     </row>
     <row r="386" spans="1:12">
       <c r="A386" s="20" t="s">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="E386" s="21">
         <f>IF(D386="?OLD","!!!","")</f>
@@ -15116,7 +15090,16 @@
     </row>
     <row r="387" spans="1:12">
       <c r="A387" s="20" t="s">
-        <v>125</v>
+        <v>298</v>
+      </c>
+      <c r="B387" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C387" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D387" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E387" s="21">
         <f>IF(D387="?OLD","!!!","")</f>
@@ -15149,11 +15132,42 @@
       <c r="L387" s="26"/>
     </row>
     <row r="388" spans="1:12">
-      <c r="A388" s="20"/>
+      <c r="A388" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="E388" s="21">
+        <f>IF(D388="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F388" s="22" t="str">
+        <f>IF(OR(E388="",E388="!!!"),"",IF(NOT(ISNA(VLOOKUP(E388,E$1:E387,1,FALSE()))),"OLD",IF(AND(E388&lt;&gt;"",E388&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G388" s="23" t="str">
+        <f>IF(OR(E388="",E388="!!!"),"",IF(OR(J388=0,AND(J388=1,K388=1),AND(J388=1,I388="SBJ"),AND(J388=1,I388=0)),"?IN_FOCUS",IF(J388&lt;=2,"?ACTIVATED",IF(J388&lt;&gt;"","?FAMILIAR",IF(F388="NEW",IF(ISNA(VLOOKUP(E388,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H388" s="24" t="str">
+        <f>IF(J388&lt;&gt;1,"",IF(I388="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I388" s="25" t="str">
+        <f>IF(OR(E388="",E388="!!!",F388="NEW"),"",INDEX(B387:B$2,-1+SUMPRODUCT(MAX(ROW(E387:E$2)*(E388=E387:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J388" s="25" t="str">
+        <f>IF(OR(E388="",E388="!!!",F388="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E388)*(E388=E$2:E388)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E387)*(E2=E$1:E387))))))</f>
+        <v> </v>
+      </c>
+      <c r="K388" s="25" t="str">
+        <f>IF(OR(E388="",E388="!!!",F388="NEW"),"",INDEX(J$1:J387,SUMPRODUCT(MAX(ROW(E$1:E387)*(E388=E$1:E387)))))</f>
+        <v> </v>
+      </c>
+      <c r="L388" s="26"/>
     </row>
     <row r="389" spans="1:12">
       <c r="A389" s="20" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E389" s="21">
         <f>IF(D389="?OLD","!!!","")</f>
@@ -15186,13 +15200,11 @@
       <c r="L389" s="26"/>
     </row>
     <row r="390" spans="1:12">
-      <c r="A390" s="20" t="s">
-        <v>296</v>
-      </c>
+      <c r="A390" s="20"/>
     </row>
     <row r="391" spans="1:12">
       <c r="A391" s="20" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E391" s="21">
         <f>IF(D391="?OLD","!!!","")</f>
@@ -15226,47 +15238,12 @@
     </row>
     <row r="392" spans="1:12">
       <c r="A392" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="E392" s="21">
-        <f>IF(D392="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F392" s="22" t="str">
-        <f>IF(OR(E392="",E392="!!!"),"",IF(NOT(ISNA(VLOOKUP(E392,E$1:E391,1,FALSE()))),"OLD",IF(AND(E392&lt;&gt;"",E392&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G392" s="23" t="str">
-        <f>IF(OR(E392="",E392="!!!"),"",IF(OR(J392=0,AND(J392=1,K392=1),AND(J392=1,I392="SBJ"),AND(J392=1,I392=0)),"?IN_FOCUS",IF(J392&lt;=2,"?ACTIVATED",IF(J392&lt;&gt;"","?FAMILIAR",IF(F392="NEW",IF(ISNA(VLOOKUP(E392,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H392" s="24" t="str">
-        <f>IF(J392&lt;&gt;1,"",IF(I392="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I392" s="25" t="str">
-        <f>IF(OR(E392="",E392="!!!",F392="NEW"),"",INDEX(B391:B$2,-1+SUMPRODUCT(MAX(ROW(E391:E$2)*(E392=E391:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J392" s="25" t="str">
-        <f>IF(OR(E392="",E392="!!!",F392="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E392)*(E392=E$2:E392)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E391)*(E2=E$1:E391))))))</f>
-        <v> </v>
-      </c>
-      <c r="K392" s="25" t="str">
-        <f>IF(OR(E392="",E392="!!!",F392="NEW"),"",INDEX(J$1:J391,SUMPRODUCT(MAX(ROW(E$1:E391)*(E392=E$1:E391)))))</f>
-        <v> </v>
-      </c>
-      <c r="L392" s="26"/>
+        <v>300</v>
+      </c>
     </row>
     <row r="393" spans="1:12">
       <c r="A393" s="20" t="s">
-        <v>298</v>
-      </c>
-      <c r="B393" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C393" s="27" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="E393" s="21">
         <f>IF(D393="?OLD","!!!","")</f>
@@ -15300,7 +15277,7 @@
     </row>
     <row r="394" spans="1:12">
       <c r="A394" s="20" t="s">
-        <v>105</v>
+        <v>301</v>
       </c>
       <c r="E394" s="21">
         <f>IF(D394="?OLD","!!!","")</f>
@@ -15334,16 +15311,13 @@
     </row>
     <row r="395" spans="1:12">
       <c r="A395" s="20" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B395" s="27" t="s">
-        <v>192</v>
+        <v>101</v>
       </c>
       <c r="C395" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D395" s="27" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="E395" s="21">
         <f>IF(D395="?OLD","!!!","")</f>
@@ -15377,7 +15351,7 @@
     </row>
     <row r="396" spans="1:12">
       <c r="A396" s="20" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E396" s="21">
         <f>IF(D396="?OLD","!!!","")</f>
@@ -15411,7 +15385,16 @@
     </row>
     <row r="397" spans="1:12">
       <c r="A397" s="20" t="s">
-        <v>106</v>
+        <v>303</v>
+      </c>
+      <c r="B397" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C397" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D397" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E397" s="21">
         <f>IF(D397="?OLD","!!!","")</f>
@@ -15445,16 +15428,7 @@
     </row>
     <row r="398" spans="1:12">
       <c r="A398" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="B398" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C398" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D398" s="27" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E398" s="21">
         <f>IF(D398="?OLD","!!!","")</f>
@@ -15488,7 +15462,7 @@
     </row>
     <row r="399" spans="1:12">
       <c r="A399" s="20" t="s">
-        <v>301</v>
+        <v>109</v>
       </c>
       <c r="E399" s="21">
         <f>IF(D399="?OLD","!!!","")</f>
@@ -15522,7 +15496,16 @@
     </row>
     <row r="400" spans="1:12">
       <c r="A400" s="20" t="s">
-        <v>302</v>
+        <v>304</v>
+      </c>
+      <c r="B400" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C400" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D400" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E400" s="21">
         <f>IF(D400="?OLD","!!!","")</f>
@@ -15556,7 +15539,7 @@
     </row>
     <row r="401" spans="1:12">
       <c r="A401" s="20" t="s">
-        <v>105</v>
+        <v>305</v>
       </c>
       <c r="E401" s="21">
         <f>IF(D401="?OLD","!!!","")</f>
@@ -15590,7 +15573,7 @@
     </row>
     <row r="402" spans="1:12">
       <c r="A402" s="20" t="s">
-        <v>269</v>
+        <v>306</v>
       </c>
       <c r="E402" s="21">
         <f>IF(D402="?OLD","!!!","")</f>
@@ -15624,16 +15607,7 @@
     </row>
     <row r="403" spans="1:12">
       <c r="A403" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B403" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C403" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D403" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E403" s="21">
         <f>IF(D403="?OLD","!!!","")</f>
@@ -15667,16 +15641,7 @@
     </row>
     <row r="404" spans="1:12">
       <c r="A404" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="B404" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C404" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="D404" s="27" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="E404" s="21">
         <f>IF(D404="?OLD","!!!","")</f>
@@ -15710,7 +15675,16 @@
     </row>
     <row r="405" spans="1:12">
       <c r="A405" s="20" t="s">
-        <v>303</v>
+        <v>139</v>
+      </c>
+      <c r="B405" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C405" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D405" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E405" s="21">
         <f>IF(D405="?OLD","!!!","")</f>
@@ -15744,16 +15718,16 @@
     </row>
     <row r="406" spans="1:12">
       <c r="A406" s="20" t="s">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="B406" s="27" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="C406" s="27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D406" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E406" s="21">
         <f>IF(D406="?OLD","!!!","")</f>
@@ -15787,7 +15761,7 @@
     </row>
     <row r="407" spans="1:12">
       <c r="A407" s="20" t="s">
-        <v>105</v>
+        <v>307</v>
       </c>
       <c r="E407" s="21">
         <f>IF(D407="?OLD","!!!","")</f>
@@ -15821,10 +15795,16 @@
     </row>
     <row r="408" spans="1:12">
       <c r="A408" s="20" t="s">
-        <v>106</v>
+        <v>308</v>
       </c>
       <c r="B408" s="27" t="s">
-        <v>107</v>
+        <v>123</v>
+      </c>
+      <c r="C408" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="D408" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E408" s="21">
         <f>IF(D408="?OLD","!!!","")</f>
@@ -15858,13 +15838,7 @@
     </row>
     <row r="409" spans="1:12">
       <c r="A409" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="B409" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C409" s="27" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="E409" s="21">
         <f>IF(D409="?OLD","!!!","")</f>
@@ -15898,13 +15872,10 @@
     </row>
     <row r="410" spans="1:12">
       <c r="A410" s="20" t="s">
-        <v>306</v>
+        <v>109</v>
       </c>
       <c r="B410" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C410" s="27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E410" s="21">
         <f>IF(D410="?OLD","!!!","")</f>
@@ -15938,7 +15909,13 @@
     </row>
     <row r="411" spans="1:12">
       <c r="A411" s="20" t="s">
-        <v>307</v>
+        <v>309</v>
+      </c>
+      <c r="B411" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C411" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="E411" s="21">
         <f>IF(D411="?OLD","!!!","")</f>
@@ -15972,7 +15949,13 @@
     </row>
     <row r="412" spans="1:12">
       <c r="A412" s="20" t="s">
-        <v>308</v>
+        <v>310</v>
+      </c>
+      <c r="B412" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="C412" s="27" t="s">
+        <v>115</v>
       </c>
       <c r="E412" s="21">
         <f>IF(D412="?OLD","!!!","")</f>
@@ -16006,7 +15989,7 @@
     </row>
     <row r="413" spans="1:12">
       <c r="A413" s="20" t="s">
-        <v>105</v>
+        <v>311</v>
       </c>
       <c r="E413" s="21">
         <f>IF(D413="?OLD","!!!","")</f>
@@ -16040,7 +16023,7 @@
     </row>
     <row r="414" spans="1:12">
       <c r="A414" s="20" t="s">
-        <v>148</v>
+        <v>312</v>
       </c>
       <c r="E414" s="21">
         <f>IF(D414="?OLD","!!!","")</f>
@@ -16074,7 +16057,7 @@
     </row>
     <row r="415" spans="1:12">
       <c r="A415" s="20" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E415" s="21">
         <f>IF(D415="?OLD","!!!","")</f>
@@ -16108,16 +16091,7 @@
     </row>
     <row r="416" spans="1:12">
       <c r="A416" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B416" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C416" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D416" s="27" t="s">
-        <v>95</v>
+        <v>152</v>
       </c>
       <c r="E416" s="21">
         <f>IF(D416="?OLD","!!!","")</f>
@@ -16151,7 +16125,7 @@
     </row>
     <row r="417" spans="1:12">
       <c r="A417" s="20" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E417" s="21">
         <f>IF(D417="?OLD","!!!","")</f>
@@ -16184,90 +16158,99 @@
       <c r="L417" s="26"/>
     </row>
     <row r="418" spans="1:12">
-      <c r="A418" s="20"/>
+      <c r="A418" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="B418" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C418" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D418" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E418" s="21">
+        <f>IF(D418="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F418" s="22" t="str">
+        <f>IF(OR(E418="",E418="!!!"),"",IF(NOT(ISNA(VLOOKUP(E418,E$1:E417,1,FALSE()))),"OLD",IF(AND(E418&lt;&gt;"",E418&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G418" s="23" t="str">
+        <f>IF(OR(E418="",E418="!!!"),"",IF(OR(J418=0,AND(J418=1,K418=1),AND(J418=1,I418="SBJ"),AND(J418=1,I418=0)),"?IN_FOCUS",IF(J418&lt;=2,"?ACTIVATED",IF(J418&lt;&gt;"","?FAMILIAR",IF(F418="NEW",IF(ISNA(VLOOKUP(E418,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H418" s="24" t="str">
+        <f>IF(J418&lt;&gt;1,"",IF(I418="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I418" s="25" t="str">
+        <f>IF(OR(E418="",E418="!!!",F418="NEW"),"",INDEX(B417:B$2,-1+SUMPRODUCT(MAX(ROW(E417:E$2)*(E418=E417:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J418" s="25" t="str">
+        <f>IF(OR(E418="",E418="!!!",F418="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E418)*(E418=E$2:E418)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E417)*(E2=E$1:E417))))))</f>
+        <v> </v>
+      </c>
+      <c r="K418" s="25" t="str">
+        <f>IF(OR(E418="",E418="!!!",F418="NEW"),"",INDEX(J$1:J417,SUMPRODUCT(MAX(ROW(E$1:E417)*(E418=E$1:E417)))))</f>
+        <v> </v>
+      </c>
+      <c r="L418" s="26"/>
     </row>
     <row r="419" spans="1:12">
       <c r="A419" s="20" t="s">
-        <v>309</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E419" s="21">
+        <f>IF(D419="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F419" s="22" t="str">
+        <f>IF(OR(E419="",E419="!!!"),"",IF(NOT(ISNA(VLOOKUP(E419,E$1:E418,1,FALSE()))),"OLD",IF(AND(E419&lt;&gt;"",E419&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G419" s="23" t="str">
+        <f>IF(OR(E419="",E419="!!!"),"",IF(OR(J419=0,AND(J419=1,K419=1),AND(J419=1,I419="SBJ"),AND(J419=1,I419=0)),"?IN_FOCUS",IF(J419&lt;=2,"?ACTIVATED",IF(J419&lt;&gt;"","?FAMILIAR",IF(F419="NEW",IF(ISNA(VLOOKUP(E419,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H419" s="24" t="str">
+        <f>IF(J419&lt;&gt;1,"",IF(I419="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I419" s="25" t="str">
+        <f>IF(OR(E419="",E419="!!!",F419="NEW"),"",INDEX(B418:B$2,-1+SUMPRODUCT(MAX(ROW(E418:E$2)*(E419=E418:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J419" s="25" t="str">
+        <f>IF(OR(E419="",E419="!!!",F419="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E419)*(E419=E$2:E419)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E418)*(E2=E$1:E418))))))</f>
+        <v> </v>
+      </c>
+      <c r="K419" s="25" t="str">
+        <f>IF(OR(E419="",E419="!!!",F419="NEW"),"",INDEX(J$1:J418,SUMPRODUCT(MAX(ROW(E$1:E418)*(E419=E$1:E418)))))</f>
+        <v> </v>
+      </c>
+      <c r="L419" s="26"/>
     </row>
     <row r="420" spans="1:12">
-      <c r="A420" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="B420" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C420" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E420" s="21">
-        <f>IF(D420="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F420" s="22" t="str">
-        <f>IF(OR(E420="",E420="!!!"),"",IF(NOT(ISNA(VLOOKUP(E420,E$1:E419,1,FALSE()))),"OLD",IF(AND(E420&lt;&gt;"",E420&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G420" s="23" t="str">
-        <f>IF(OR(E420="",E420="!!!"),"",IF(OR(J420=0,AND(J420=1,K420=1),AND(J420=1,I420="SBJ"),AND(J420=1,I420=0)),"?IN_FOCUS",IF(J420&lt;=2,"?ACTIVATED",IF(J420&lt;&gt;"","?FAMILIAR",IF(F420="NEW",IF(ISNA(VLOOKUP(E420,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H420" s="24" t="str">
-        <f>IF(J420&lt;&gt;1,"",IF(I420="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I420" s="25" t="str">
-        <f>IF(OR(E420="",E420="!!!",F420="NEW"),"",INDEX(B419:B$2,-1+SUMPRODUCT(MAX(ROW(E419:E$2)*(E420=E419:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J420" s="25" t="str">
-        <f>IF(OR(E420="",E420="!!!",F420="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E420)*(E420=E$2:E420)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E419)*(E2=E$1:E419))))))</f>
-        <v> </v>
-      </c>
-      <c r="K420" s="25" t="str">
-        <f>IF(OR(E420="",E420="!!!",F420="NEW"),"",INDEX(J$1:J419,SUMPRODUCT(MAX(ROW(E$1:E419)*(E420=E$1:E419)))))</f>
-        <v> </v>
-      </c>
-      <c r="L420" s="26"/>
+      <c r="A420" s="20"/>
     </row>
     <row r="421" spans="1:12">
       <c r="A421" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="E421" s="21">
-        <f>IF(D421="?OLD","!!!","")</f>
-        <v/>
-      </c>
-      <c r="F421" s="22" t="str">
-        <f>IF(OR(E421="",E421="!!!"),"",IF(NOT(ISNA(VLOOKUP(E421,E$1:E420,1,FALSE()))),"OLD",IF(AND(E421&lt;&gt;"",E421&lt;&gt;"!!!"),"NEW","")))</f>
-        <v> </v>
-      </c>
-      <c r="G421" s="23" t="str">
-        <f>IF(OR(E421="",E421="!!!"),"",IF(OR(J421=0,AND(J421=1,K421=1),AND(J421=1,I421="SBJ"),AND(J421=1,I421=0)),"?IN_FOCUS",IF(J421&lt;=2,"?ACTIVATED",IF(J421&lt;&gt;"","?FAMILIAR",IF(F421="NEW",IF(ISNA(VLOOKUP(E421,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
-        <v> </v>
-      </c>
-      <c r="H421" s="24" t="str">
-        <f>IF(J421&lt;&gt;1,"",IF(I421="SBJ","CB","?"))</f>
-        <v> </v>
-      </c>
-      <c r="I421" s="25" t="str">
-        <f>IF(OR(E421="",E421="!!!",F421="NEW"),"",INDEX(B420:B$2,-1+SUMPRODUCT(MAX(ROW(E420:E$2)*(E421=E420:E$2)))))</f>
-        <v> </v>
-      </c>
-      <c r="J421" s="25" t="str">
-        <f>IF(OR(E421="",E421="!!!",F421="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E421)*(E421=E$2:E421)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E420)*(E2=E$1:E420))))))</f>
-        <v> </v>
-      </c>
-      <c r="K421" s="25" t="str">
-        <f>IF(OR(E421="",E421="!!!",F421="NEW"),"",INDEX(J$1:J420,SUMPRODUCT(MAX(ROW(E$1:E420)*(E421=E$1:E420)))))</f>
-        <v> </v>
-      </c>
-      <c r="L421" s="26"/>
+        <v>313</v>
+      </c>
     </row>
     <row r="422" spans="1:12">
       <c r="A422" s="20" t="s">
-        <v>106</v>
+        <v>314</v>
+      </c>
+      <c r="B422" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C422" s="27" t="s">
+        <v>145</v>
       </c>
       <c r="E422" s="21">
         <f>IF(D422="?OLD","!!!","")</f>
@@ -16301,16 +16284,7 @@
     </row>
     <row r="423" spans="1:12">
       <c r="A423" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B423" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C423" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D423" s="27" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E423" s="21">
         <f>IF(D423="?OLD","!!!","")</f>
@@ -16344,13 +16318,7 @@
     </row>
     <row r="424" spans="1:12">
       <c r="A424" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="B424" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="C424" s="27" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="E424" s="21">
         <f>IF(D424="?OLD","!!!","")</f>
@@ -16384,7 +16352,16 @@
     </row>
     <row r="425" spans="1:12">
       <c r="A425" s="20" t="s">
-        <v>118</v>
+        <v>315</v>
+      </c>
+      <c r="B425" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C425" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D425" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E425" s="21">
         <f>IF(D425="?OLD","!!!","")</f>
@@ -16418,16 +16395,13 @@
     </row>
     <row r="426" spans="1:12">
       <c r="A426" s="20" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="B426" s="27" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C426" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D426" s="27" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="E426" s="21">
         <f>IF(D426="?OLD","!!!","")</f>
@@ -16461,7 +16435,7 @@
     </row>
     <row r="427" spans="1:12">
       <c r="A427" s="20" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="E427" s="21">
         <f>IF(D427="?OLD","!!!","")</f>
@@ -16495,7 +16469,16 @@
     </row>
     <row r="428" spans="1:12">
       <c r="A428" s="20" t="s">
-        <v>105</v>
+        <v>316</v>
+      </c>
+      <c r="B428" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C428" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D428" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E428" s="21">
         <f>IF(D428="?OLD","!!!","")</f>
@@ -16529,7 +16512,7 @@
     </row>
     <row r="429" spans="1:12">
       <c r="A429" s="20" t="s">
-        <v>313</v>
+        <v>200</v>
       </c>
       <c r="E429" s="21">
         <f>IF(D429="?OLD","!!!","")</f>
@@ -16563,13 +16546,7 @@
     </row>
     <row r="430" spans="1:12">
       <c r="A430" s="20" t="s">
-        <v>314</v>
-      </c>
-      <c r="B430" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="C430" s="27" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E430" s="21">
         <f>IF(D430="?OLD","!!!","")</f>
@@ -16603,7 +16580,7 @@
     </row>
     <row r="431" spans="1:12">
       <c r="A431" s="20" t="s">
-        <v>222</v>
+        <v>317</v>
       </c>
       <c r="E431" s="21">
         <f>IF(D431="?OLD","!!!","")</f>
@@ -16637,16 +16614,13 @@
     </row>
     <row r="432" spans="1:12">
       <c r="A432" s="20" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B432" s="27" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="C432" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="D432" s="27" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E432" s="21">
         <f>IF(D432="?OLD","!!!","")</f>
@@ -16680,7 +16654,7 @@
     </row>
     <row r="433" spans="1:12">
       <c r="A433" s="20" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="E433" s="21">
         <f>IF(D433="?OLD","!!!","")</f>
@@ -16714,16 +16688,16 @@
     </row>
     <row r="434" spans="1:12">
       <c r="A434" s="20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B434" s="27" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="C434" s="27" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="D434" s="27" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E434" s="21">
         <f>IF(D434="?OLD","!!!","")</f>
@@ -16757,7 +16731,7 @@
     </row>
     <row r="435" spans="1:12">
       <c r="A435" s="20" t="s">
-        <v>317</v>
+        <v>134</v>
       </c>
       <c r="E435" s="21">
         <f>IF(D435="?OLD","!!!","")</f>
@@ -16791,7 +16765,16 @@
     </row>
     <row r="436" spans="1:12">
       <c r="A436" s="20" t="s">
-        <v>106</v>
+        <v>320</v>
+      </c>
+      <c r="B436" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="C436" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D436" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E436" s="21">
         <f>IF(D436="?OLD","!!!","")</f>
@@ -16825,16 +16808,7 @@
     </row>
     <row r="437" spans="1:12">
       <c r="A437" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="B437" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C437" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="D437" s="27" t="s">
-        <v>95</v>
+        <v>321</v>
       </c>
       <c r="E437" s="21">
         <f>IF(D437="?OLD","!!!","")</f>
@@ -16868,7 +16842,7 @@
     </row>
     <row r="438" spans="1:12">
       <c r="A438" s="20" t="s">
-        <v>319</v>
+        <v>109</v>
       </c>
       <c r="E438" s="21">
         <f>IF(D438="?OLD","!!!","")</f>
@@ -16902,13 +16876,16 @@
     </row>
     <row r="439" spans="1:12">
       <c r="A439" s="20" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B439" s="27" t="s">
-        <v>321</v>
+        <v>114</v>
       </c>
       <c r="C439" s="27" t="s">
-        <v>165</v>
+        <v>124</v>
+      </c>
+      <c r="D439" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="E439" s="21">
         <f>IF(D439="?OLD","!!!","")</f>
@@ -16942,7 +16919,7 @@
     </row>
     <row r="440" spans="1:12">
       <c r="A440" s="20" t="s">
-        <v>125</v>
+        <v>323</v>
       </c>
       <c r="E440" s="21">
         <f>IF(D440="?OLD","!!!","")</f>
@@ -16975,7 +16952,81 @@
       <c r="L440" s="26"/>
     </row>
     <row r="441" spans="1:12">
-      <c r="A441" s="20"/>
+      <c r="A441" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="B441" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="C441" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E441" s="21">
+        <f>IF(D441="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F441" s="22" t="str">
+        <f>IF(OR(E441="",E441="!!!"),"",IF(NOT(ISNA(VLOOKUP(E441,E$1:E440,1,FALSE()))),"OLD",IF(AND(E441&lt;&gt;"",E441&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G441" s="23" t="str">
+        <f>IF(OR(E441="",E441="!!!"),"",IF(OR(J441=0,AND(J441=1,K441=1),AND(J441=1,I441="SBJ"),AND(J441=1,I441=0)),"?IN_FOCUS",IF(J441&lt;=2,"?ACTIVATED",IF(J441&lt;&gt;"","?FAMILIAR",IF(F441="NEW",IF(ISNA(VLOOKUP(E441,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H441" s="24" t="str">
+        <f>IF(J441&lt;&gt;1,"",IF(I441="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I441" s="25" t="str">
+        <f>IF(OR(E441="",E441="!!!",F441="NEW"),"",INDEX(B440:B$2,-1+SUMPRODUCT(MAX(ROW(E440:E$2)*(E441=E440:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J441" s="25" t="str">
+        <f>IF(OR(E441="",E441="!!!",F441="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E441)*(E441=E$2:E441)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E440)*(E2=E$1:E440))))))</f>
+        <v> </v>
+      </c>
+      <c r="K441" s="25" t="str">
+        <f>IF(OR(E441="",E441="!!!",F441="NEW"),"",INDEX(J$1:J440,SUMPRODUCT(MAX(ROW(E$1:E440)*(E441=E$1:E440)))))</f>
+        <v> </v>
+      </c>
+      <c r="L441" s="26"/>
+    </row>
+    <row r="442" spans="1:12">
+      <c r="A442" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="E442" s="21">
+        <f>IF(D442="?OLD","!!!","")</f>
+        <v/>
+      </c>
+      <c r="F442" s="22" t="str">
+        <f>IF(OR(E442="",E442="!!!"),"",IF(NOT(ISNA(VLOOKUP(E442,E$1:E441,1,FALSE()))),"OLD",IF(AND(E442&lt;&gt;"",E442&lt;&gt;"!!!"),"NEW","")))</f>
+        <v> </v>
+      </c>
+      <c r="G442" s="23" t="str">
+        <f>IF(OR(E442="",E442="!!!"),"",IF(OR(J442=0,AND(J442=1,K442=1),AND(J442=1,I442="SBJ"),AND(J442=1,I442=0)),"?IN_FOCUS",IF(J442&lt;=2,"?ACTIVATED",IF(J442&lt;&gt;"","?FAMILIAR",IF(F442="NEW",IF(ISNA(VLOOKUP(E442,#REF!,1,FALSE())),"?TYPE_IDENTIFIABLE","?REFERENTIAL"),"_")))))</f>
+        <v> </v>
+      </c>
+      <c r="H442" s="24" t="str">
+        <f>IF(J442&lt;&gt;1,"",IF(I442="SBJ","CB","?"))</f>
+        <v> </v>
+      </c>
+      <c r="I442" s="25" t="str">
+        <f>IF(OR(E442="",E442="!!!",F442="NEW"),"",INDEX(B441:B$2,-1+SUMPRODUCT(MAX(ROW(E441:E$2)*(E442=E441:E$2)))))</f>
+        <v> </v>
+      </c>
+      <c r="J442" s="25" t="str">
+        <f>IF(OR(E442="",E442="!!!",F442="NEW"),"",COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$2:E442)*(E442=E$2:E442)))))-COUNTBLANK(OFFSET(A$1,,,SUMPRODUCT(MAX(ROW(E$1:E441)*(E2=E$1:E441))))))</f>
+        <v> </v>
+      </c>
+      <c r="K442" s="25" t="str">
+        <f>IF(OR(E442="",E442="!!!",F442="NEW"),"",INDEX(J$1:J441,SUMPRODUCT(MAX(ROW(E$1:E441)*(E442=E$1:E441)))))</f>
+        <v> </v>
+      </c>
+      <c r="L442" s="26"/>
+    </row>
+    <row r="443" spans="1:12">
+      <c r="A443" s="20"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
